--- a/data/df_dimless.xlsx
+++ b/data/df_dimless.xlsx
@@ -553,13 +553,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1387.532037221465</v>
+        <v>1387.532037221464</v>
       </c>
       <c r="N2" t="n">
-        <v>1289.747994202608</v>
+        <v>1289.747994202607</v>
       </c>
       <c r="O2" t="n">
-        <v>219.1861889077352</v>
+        <v>219.186188907735</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -606,13 +606,13 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1387.348917089269</v>
+        <v>1387.348917089267</v>
       </c>
       <c r="N3" t="n">
-        <v>1289.407586583955</v>
+        <v>1289.407586583953</v>
       </c>
       <c r="O3" t="n">
-        <v>219.1500305158514</v>
+        <v>219.1500305158511</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -659,13 +659,13 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1387.348917089269</v>
+        <v>1387.348917089267</v>
       </c>
       <c r="N4" t="n">
-        <v>1289.407586583955</v>
+        <v>1289.407586583953</v>
       </c>
       <c r="O4" t="n">
-        <v>219.1500305158514</v>
+        <v>219.1500305158511</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -712,13 +712,13 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1329.06481460242</v>
+        <v>1329.064814602419</v>
       </c>
       <c r="N5" t="n">
-        <v>1230.678129894624</v>
+        <v>1230.678129894622</v>
       </c>
       <c r="O5" t="n">
-        <v>211.8160093718203</v>
+        <v>211.8160093718202</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -765,13 +765,13 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1329.055807057854</v>
+        <v>1329.055807057855</v>
       </c>
       <c r="N6" t="n">
-        <v>1230.661448465072</v>
+        <v>1230.661448465074</v>
       </c>
       <c r="O6" t="n">
-        <v>211.8142149328781</v>
+        <v>211.8142149328785</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -927,10 +927,10 @@
         <v>1436.174341095939</v>
       </c>
       <c r="N9" t="n">
-        <v>1338.849840108946</v>
+        <v>1338.849840108945</v>
       </c>
       <c r="O9" t="n">
-        <v>225.2515179603793</v>
+        <v>225.2515179603792</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
@@ -980,7 +980,7 @@
         <v>10559.03613176333</v>
       </c>
       <c r="N10" t="n">
-        <v>556.5605742545657</v>
+        <v>556.5605742545655</v>
       </c>
       <c r="O10" t="n">
         <v>239.1455413291526</v>
@@ -1189,13 +1189,13 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>11159.13794680485</v>
+        <v>11159.13794680484</v>
       </c>
       <c r="N14" t="n">
-        <v>590.6889397706796</v>
+        <v>590.6889397706789</v>
       </c>
       <c r="O14" t="n">
-        <v>249.796921089002</v>
+        <v>249.7969210890018</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
@@ -1245,7 +1245,7 @@
         <v>11642.62112144351</v>
       </c>
       <c r="N15" t="n">
-        <v>618.1759668513675</v>
+        <v>618.1759668513677</v>
       </c>
       <c r="O15" t="n">
         <v>258.2668999202124</v>
@@ -1295,13 +1295,13 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>11159.13794680485</v>
+        <v>11159.13794680484</v>
       </c>
       <c r="N16" t="n">
-        <v>590.6889397706796</v>
+        <v>590.6889397706789</v>
       </c>
       <c r="O16" t="n">
-        <v>249.796921089002</v>
+        <v>249.7969210890018</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
@@ -1351,7 +1351,7 @@
         <v>11816.57919934269</v>
       </c>
       <c r="N17" t="n">
-        <v>628.0638020254522</v>
+        <v>628.0638020254526</v>
       </c>
       <c r="O17" t="n">
         <v>261.2912247074408</v>
@@ -1404,7 +1404,7 @@
         <v>11816.57919934269</v>
       </c>
       <c r="N18" t="n">
-        <v>628.0638020254522</v>
+        <v>628.0638020254526</v>
       </c>
       <c r="O18" t="n">
         <v>261.2912247074408</v>
@@ -1457,10 +1457,10 @@
         <v>10713.9660997614</v>
       </c>
       <c r="N19" t="n">
-        <v>565.3727580378978</v>
+        <v>565.3727580378982</v>
       </c>
       <c r="O19" t="n">
-        <v>241.9106599551154</v>
+        <v>241.9106599551155</v>
       </c>
       <c r="P19" t="n">
         <v>1</v>
@@ -1510,10 +1510,10 @@
         <v>11178.48505588814</v>
       </c>
       <c r="N20" t="n">
-        <v>591.7890221789754</v>
+        <v>591.7890221789756</v>
       </c>
       <c r="O20" t="n">
-        <v>250.137721736856</v>
+        <v>250.1377217368561</v>
       </c>
       <c r="P20" t="n">
         <v>1</v>
@@ -1560,13 +1560,13 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>5822.305198084934</v>
+        <v>5822.305198084933</v>
       </c>
       <c r="N21" t="n">
-        <v>624.15911589722</v>
+        <v>624.1591158972197</v>
       </c>
       <c r="O21" t="n">
-        <v>218.2334913295999</v>
+        <v>218.2334913295998</v>
       </c>
       <c r="P21" t="n">
         <v>1</v>
@@ -1666,13 +1666,13 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>5988.738467028608</v>
+        <v>5988.738467028606</v>
       </c>
       <c r="N23" t="n">
-        <v>643.3115194907909</v>
+        <v>643.3115194907903</v>
       </c>
       <c r="O23" t="n">
-        <v>223.1230823908008</v>
+        <v>223.1230823908007</v>
       </c>
       <c r="P23" t="n">
         <v>1</v>
@@ -1719,13 +1719,13 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>6175.805899755555</v>
+        <v>6175.80589975555</v>
       </c>
       <c r="N24" t="n">
-        <v>664.8274152958041</v>
+        <v>664.8274152958029</v>
       </c>
       <c r="O24" t="n">
-        <v>228.5745479399449</v>
+        <v>228.5745479399446</v>
       </c>
       <c r="P24" t="n">
         <v>1</v>
@@ -1772,10 +1772,10 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>6258.876012810141</v>
+        <v>6258.876012810144</v>
       </c>
       <c r="N25" t="n">
-        <v>674.3766138721305</v>
+        <v>674.3766138721312</v>
       </c>
       <c r="O25" t="n">
         <v>230.980510977413</v>
@@ -1825,13 +1825,13 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>6030.421339369627</v>
+        <v>6030.421339369632</v>
       </c>
       <c r="N26" t="n">
-        <v>648.1164533923055</v>
+        <v>648.1164533923064</v>
       </c>
       <c r="O26" t="n">
-        <v>224.3434724025128</v>
+        <v>224.343472402513</v>
       </c>
       <c r="P26" t="n">
         <v>1</v>
@@ -1878,13 +1878,13 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>6019.988702760943</v>
+        <v>6019.98870276094</v>
       </c>
       <c r="N27" t="n">
-        <v>646.9126275152167</v>
+        <v>646.9126275152162</v>
       </c>
       <c r="O27" t="n">
-        <v>224.0380238706048</v>
+        <v>224.0380238706047</v>
       </c>
       <c r="P27" t="n">
         <v>1</v>
@@ -1931,13 +1931,13 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>5489.299013966282</v>
+        <v>5489.299013966283</v>
       </c>
       <c r="N28" t="n">
-        <v>585.8414157273763</v>
+        <v>585.8414157273768</v>
       </c>
       <c r="O28" t="n">
-        <v>208.3383677989757</v>
+        <v>208.3383677989758</v>
       </c>
       <c r="P28" t="n">
         <v>1</v>
@@ -1984,13 +1984,13 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>5364.205174161519</v>
+        <v>5364.205174161514</v>
       </c>
       <c r="N29" t="n">
-        <v>571.4326579115112</v>
+        <v>571.4326579115102</v>
       </c>
       <c r="O29" t="n">
-        <v>204.5779741823429</v>
+        <v>204.5779741823427</v>
       </c>
       <c r="P29" t="n">
         <v>1</v>
@@ -2037,13 +2037,13 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1943.409875762161</v>
+        <v>1943.409875762162</v>
       </c>
       <c r="N30" t="n">
-        <v>727.1768060673546</v>
+        <v>727.1768060673548</v>
       </c>
       <c r="O30" t="n">
-        <v>179.044551874429</v>
+        <v>179.0445518744291</v>
       </c>
       <c r="P30" t="n">
         <v>1</v>
@@ -2090,13 +2090,13 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1943.501941312142</v>
+        <v>1943.501941312144</v>
       </c>
       <c r="N31" t="n">
-        <v>727.2457050877699</v>
+        <v>727.2457050877714</v>
       </c>
       <c r="O31" t="n">
-        <v>179.0551543295231</v>
+        <v>179.0551543295233</v>
       </c>
       <c r="P31" t="n">
         <v>1</v>
@@ -2143,13 +2143,13 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2056.36664742069</v>
+        <v>2056.366647420689</v>
       </c>
       <c r="N32" t="n">
-        <v>772.222956189772</v>
+        <v>772.222956189771</v>
       </c>
       <c r="O32" t="n">
-        <v>187.1313246297634</v>
+        <v>187.1313246297632</v>
       </c>
       <c r="P32" t="n">
         <v>1</v>
@@ -2196,13 +2196,13 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>2003.213017927353</v>
+        <v>2003.213017927355</v>
       </c>
       <c r="N33" t="n">
-        <v>751.024216738248</v>
+        <v>751.024216738249</v>
       </c>
       <c r="O33" t="n">
-        <v>183.340644614671</v>
+        <v>183.3406446146712</v>
       </c>
       <c r="P33" t="n">
         <v>1</v>
@@ -2249,13 +2249,13 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>2066.311777398583</v>
+        <v>2066.311777398581</v>
       </c>
       <c r="N34" t="n">
-        <v>776.182263511009</v>
+        <v>776.1822635110078</v>
       </c>
       <c r="O34" t="n">
-        <v>187.8368601384674</v>
+        <v>187.8368601384672</v>
       </c>
       <c r="P34" t="n">
         <v>1</v>
@@ -2358,7 +2358,7 @@
         <v>2056.343681927162</v>
       </c>
       <c r="N36" t="n">
-        <v>772.2057079210401</v>
+        <v>772.2057079210402</v>
       </c>
       <c r="O36" t="n">
         <v>187.1287122811639</v>
@@ -2408,10 +2408,10 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1914.174699069509</v>
+        <v>1914.174699069508</v>
       </c>
       <c r="N37" t="n">
-        <v>715.5216293973443</v>
+        <v>715.5216293973439</v>
       </c>
       <c r="O37" t="n">
         <v>176.9321586604406</v>
@@ -2464,7 +2464,7 @@
         <v>1914.141823434072</v>
       </c>
       <c r="N38" t="n">
-        <v>715.4970516759453</v>
+        <v>715.4970516759455</v>
       </c>
       <c r="O38" t="n">
         <v>176.9283601927119</v>
@@ -2514,13 +2514,13 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>573.0270295255189</v>
+        <v>573.0270295255191</v>
       </c>
       <c r="N39" t="n">
-        <v>728.9557054484884</v>
+        <v>728.9557054484891</v>
       </c>
       <c r="O39" t="n">
-        <v>132.0974234264458</v>
+        <v>132.0974234264459</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -2567,13 +2567,13 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>644.7481096021464</v>
+        <v>644.7481096021457</v>
       </c>
       <c r="N40" t="n">
-        <v>826.4327632207645</v>
+        <v>826.4327632207627</v>
       </c>
       <c r="O40" t="n">
-        <v>144.860934465044</v>
+        <v>144.8609344650438</v>
       </c>
       <c r="P40" t="n">
         <v>1</v>
@@ -2623,7 +2623,7 @@
         <v>573.0025733154055</v>
       </c>
       <c r="N41" t="n">
-        <v>728.8934846018353</v>
+        <v>728.8934846018351</v>
       </c>
       <c r="O41" t="n">
         <v>132.0903762346441</v>
@@ -2673,13 +2673,13 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>644.7351762923781</v>
+        <v>644.7351762923776</v>
       </c>
       <c r="N42" t="n">
-        <v>826.3996079355695</v>
+        <v>826.399607935568</v>
       </c>
       <c r="O42" t="n">
-        <v>144.857302180953</v>
+        <v>144.8573021809528</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
@@ -2726,10 +2726,10 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>644.782549273439</v>
+        <v>644.7825492734388</v>
       </c>
       <c r="N43" t="n">
-        <v>826.5210545470907</v>
+        <v>826.5210545470901</v>
       </c>
       <c r="O43" t="n">
         <v>144.8706068398104</v>
@@ -2779,13 +2779,13 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>597.5724758387255</v>
+        <v>597.5724758387258</v>
       </c>
       <c r="N44" t="n">
-        <v>762.2523211998324</v>
+        <v>762.2523211998333</v>
       </c>
       <c r="O44" t="n">
-        <v>136.5045174924876</v>
+        <v>136.5045174924877</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
@@ -2832,13 +2832,13 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>644.7351762923781</v>
+        <v>644.7351762923776</v>
       </c>
       <c r="N45" t="n">
-        <v>826.3996079355695</v>
+        <v>826.399607935568</v>
       </c>
       <c r="O45" t="n">
-        <v>144.857302180953</v>
+        <v>144.8573021809528</v>
       </c>
       <c r="P45" t="n">
         <v>0</v>
@@ -2885,10 +2885,10 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>568.880228242281</v>
+        <v>568.8802282422809</v>
       </c>
       <c r="N46" t="n">
-        <v>723.2652406543583</v>
+        <v>723.2652406543581</v>
       </c>
       <c r="O46" t="n">
         <v>131.3421154420951</v>
@@ -2938,13 +2938,13 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>660.3398740106061</v>
+        <v>660.3398740106055</v>
       </c>
       <c r="N47" t="n">
-        <v>847.9039284983245</v>
+        <v>847.903928498323</v>
       </c>
       <c r="O47" t="n">
-        <v>147.6098042662321</v>
+        <v>147.609804266232</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
@@ -2991,13 +2991,13 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>660.1887126644891</v>
+        <v>660.1887126644882</v>
       </c>
       <c r="N48" t="n">
-        <v>847.5157779890606</v>
+        <v>847.5157779890585</v>
       </c>
       <c r="O48" t="n">
-        <v>147.5675679514825</v>
+        <v>147.5675679514823</v>
       </c>
       <c r="P48" t="n">
         <v>1</v>
@@ -3044,13 +3044,13 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>660.272420929556</v>
+        <v>660.2724209295556</v>
       </c>
       <c r="N49" t="n">
-        <v>847.7307122091975</v>
+        <v>847.7307122091963</v>
       </c>
       <c r="O49" t="n">
-        <v>147.5909567580289</v>
+        <v>147.5909567580288</v>
       </c>
       <c r="P49" t="n">
         <v>1</v>
@@ -3097,13 +3097,13 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>613.025081738245</v>
+        <v>613.0250817382458</v>
       </c>
       <c r="N50" t="n">
-        <v>784.5813545230259</v>
+        <v>784.5813545230279</v>
       </c>
       <c r="O50" t="n">
-        <v>139.3761784549297</v>
+        <v>139.37617845493</v>
       </c>
       <c r="P50" t="n">
         <v>0</v>
@@ -3150,13 +3150,13 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>624.3038416213888</v>
+        <v>624.30384162139</v>
       </c>
       <c r="N51" t="n">
-        <v>803.6402323776789</v>
+        <v>803.6402323776821</v>
       </c>
       <c r="O51" t="n">
-        <v>141.7032585168573</v>
+        <v>141.7032585168576</v>
       </c>
       <c r="P51" t="n">
         <v>0</v>
@@ -3203,13 +3203,13 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>564.9288544316925</v>
+        <v>564.9288544316926</v>
       </c>
       <c r="N52" t="n">
-        <v>722.9568260698065</v>
+        <v>722.9568260698068</v>
       </c>
       <c r="O52" t="n">
-        <v>131.0854896577846</v>
+        <v>131.0854896577847</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
@@ -3256,10 +3256,10 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>596.5321676374992</v>
+        <v>596.5321676374996</v>
       </c>
       <c r="N53" t="n">
-        <v>765.9838344436033</v>
+        <v>765.983834443604</v>
       </c>
       <c r="O53" t="n">
         <v>136.7786361743088</v>
@@ -3309,13 +3309,13 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>596.3367675144747</v>
+        <v>596.3367675144748</v>
       </c>
       <c r="N54" t="n">
-        <v>765.4821051820511</v>
+        <v>765.4821051820513</v>
       </c>
       <c r="O54" t="n">
-        <v>136.7226344417608</v>
+        <v>136.7226344417609</v>
       </c>
       <c r="P54" t="n">
         <v>0</v>
@@ -3362,13 +3362,13 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>653.3073139426007</v>
+        <v>653.3073139425998</v>
       </c>
       <c r="N55" t="n">
-        <v>842.9846231629863</v>
+        <v>842.9846231629842</v>
       </c>
       <c r="O55" t="n">
-        <v>146.7875448012002</v>
+        <v>146.7875448011999</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
@@ -3415,13 +3415,13 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>653.7414899903989</v>
+        <v>653.7414899903974</v>
       </c>
       <c r="N56" t="n">
-        <v>844.1054596939928</v>
+        <v>844.1054596939891</v>
       </c>
       <c r="O56" t="n">
-        <v>146.9094953139749</v>
+        <v>146.9094953139745</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
@@ -3471,10 +3471,10 @@
         <v>536.3849219291579</v>
       </c>
       <c r="N57" t="n">
-        <v>684.3326627010335</v>
+        <v>684.3326627010339</v>
       </c>
       <c r="O57" t="n">
-        <v>125.8933455362902</v>
+        <v>125.8933455362903</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>
@@ -3524,7 +3524,7 @@
         <v>600.6366916857025</v>
       </c>
       <c r="N58" t="n">
-        <v>771.3257762383396</v>
+        <v>771.3257762383397</v>
       </c>
       <c r="O58" t="n">
         <v>137.4902454140887</v>
@@ -3574,13 +3574,13 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>609.9581507198722</v>
+        <v>609.9581507198717</v>
       </c>
       <c r="N59" t="n">
-        <v>784.1247709482526</v>
+        <v>784.1247709482514</v>
       </c>
       <c r="O59" t="n">
-        <v>139.1610178517212</v>
+        <v>139.1610178517211</v>
       </c>
       <c r="P59" t="n">
         <v>0</v>
@@ -3627,13 +3627,13 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>530.0462058785515</v>
+        <v>530.0462058785516</v>
       </c>
       <c r="N60" t="n">
-        <v>675.979542204431</v>
+        <v>675.9795422044314</v>
       </c>
       <c r="O60" t="n">
-        <v>124.7513370237171</v>
+        <v>124.7513370237172</v>
       </c>
       <c r="P60" t="n">
         <v>1</v>
@@ -3680,13 +3680,13 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>527.1250213110859</v>
+        <v>527.1250213110864</v>
       </c>
       <c r="N61" t="n">
-        <v>668.5491724735278</v>
+        <v>668.5491724735291</v>
       </c>
       <c r="O61" t="n">
-        <v>123.8925197165168</v>
+        <v>123.8925197165169</v>
       </c>
       <c r="P61" t="n">
         <v>0</v>
@@ -3733,13 +3733,13 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>656.8296253734779</v>
+        <v>656.8296253734787</v>
       </c>
       <c r="N62" t="n">
-        <v>845.081757316831</v>
+        <v>845.0817573168326</v>
       </c>
       <c r="O62" t="n">
-        <v>147.167714903121</v>
+        <v>147.1677149031212</v>
       </c>
       <c r="P62" t="n">
         <v>1</v>
@@ -3786,13 +3786,13 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>656.8296778026786</v>
+        <v>656.829677802677</v>
       </c>
       <c r="N63" t="n">
-        <v>845.0818922284153</v>
+        <v>845.0818922284112</v>
       </c>
       <c r="O63" t="n">
-        <v>147.1677295870768</v>
+        <v>147.1677295870763</v>
       </c>
       <c r="P63" t="n">
         <v>0</v>
@@ -3839,10 +3839,10 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>630.1909892876124</v>
+        <v>630.1909892876123</v>
       </c>
       <c r="N64" t="n">
-        <v>808.8515161343175</v>
+        <v>808.851516134317</v>
       </c>
       <c r="O64" t="n">
         <v>142.4959264327788</v>
@@ -3892,13 +3892,13 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>621.9906451036328</v>
+        <v>621.9906451036319</v>
       </c>
       <c r="N65" t="n">
-        <v>797.6959030863488</v>
+        <v>797.6959030863468</v>
       </c>
       <c r="O65" t="n">
-        <v>141.047256773434</v>
+        <v>141.0472567734338</v>
       </c>
       <c r="P65" t="n">
         <v>1</v>
@@ -3945,10 +3945,10 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>639.4144356089646</v>
+        <v>639.4144356089647</v>
       </c>
       <c r="N66" t="n">
-        <v>821.3977692631046</v>
+        <v>821.3977692631048</v>
       </c>
       <c r="O66" t="n">
         <v>144.1193745618223</v>
@@ -4051,13 +4051,13 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>616.8648971160867</v>
+        <v>616.8648971160861</v>
       </c>
       <c r="N68" t="n">
-        <v>790.7227951380105</v>
+        <v>790.7227951380089</v>
       </c>
       <c r="O68" t="n">
-        <v>140.1392031734207</v>
+        <v>140.1392031734206</v>
       </c>
       <c r="P68" t="n">
         <v>1</v>
@@ -4104,10 +4104,10 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>601.4816932884236</v>
+        <v>601.4816932884235</v>
       </c>
       <c r="N69" t="n">
-        <v>769.790714217374</v>
+        <v>769.7907142173738</v>
       </c>
       <c r="O69" t="n">
         <v>137.4016466482886</v>
@@ -4157,13 +4157,13 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>632.2411167249263</v>
+        <v>632.2411167249264</v>
       </c>
       <c r="N70" t="n">
-        <v>811.6406809046632</v>
+        <v>811.6406809046638</v>
       </c>
       <c r="O70" t="n">
-        <v>142.8573491977932</v>
+        <v>142.8573491977933</v>
       </c>
       <c r="P70" t="n">
         <v>1</v>
@@ -4213,7 +4213,7 @@
         <v>12183.66624837616</v>
       </c>
       <c r="N71" t="n">
-        <v>648.9255661281769</v>
+        <v>648.9255661281766</v>
       </c>
       <c r="O71" t="n">
         <v>267.6344041068228</v>
@@ -4372,10 +4372,10 @@
         <v>11951.846303411</v>
       </c>
       <c r="N74" t="n">
-        <v>635.7516750332659</v>
+        <v>635.7516750332665</v>
       </c>
       <c r="O74" t="n">
-        <v>263.6346601006122</v>
+        <v>263.6346601006123</v>
       </c>
       <c r="P74" t="n">
         <v>1</v>
@@ -4422,13 +4422,13 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>12762.86609614997</v>
+        <v>12762.86609614996</v>
       </c>
       <c r="N75" t="n">
-        <v>681.831902463258</v>
+        <v>681.8319024632571</v>
       </c>
       <c r="O75" t="n">
-        <v>277.5400818648338</v>
+        <v>277.5400818648336</v>
       </c>
       <c r="P75" t="n">
         <v>1</v>
@@ -4475,10 +4475,10 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>13110.15981450545</v>
+        <v>13110.15981450544</v>
       </c>
       <c r="N76" t="n">
-        <v>701.5570587484616</v>
+        <v>701.5570587484615</v>
       </c>
       <c r="O76" t="n">
         <v>283.4219591648356</v>
@@ -4531,10 +4531,10 @@
         <v>12569.85328475317</v>
       </c>
       <c r="N77" t="n">
-        <v>670.8675274276034</v>
+        <v>670.8675274276031</v>
       </c>
       <c r="O77" t="n">
-        <v>274.252716241285</v>
+        <v>274.2527162412849</v>
       </c>
       <c r="P77" t="n">
         <v>1</v>
@@ -4581,10 +4581,10 @@
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>588.8970171880881</v>
+        <v>588.8970171880882</v>
       </c>
       <c r="N78" t="n">
-        <v>752.3371574868842</v>
+        <v>752.3371574868843</v>
       </c>
       <c r="O78" t="n">
         <v>135.1188980086976</v>
@@ -4634,13 +4634,13 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>613.515381376037</v>
+        <v>613.5153813760371</v>
       </c>
       <c r="N79" t="n">
-        <v>785.8368783167556</v>
+        <v>785.8368783167559</v>
       </c>
       <c r="O79" t="n">
-        <v>139.5155343361459</v>
+        <v>139.515534336146</v>
       </c>
       <c r="P79" t="n">
         <v>1</v>
@@ -4740,13 +4740,13 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>586.1659567410511</v>
+        <v>586.1659567410505</v>
       </c>
       <c r="N81" t="n">
-        <v>748.6266462815166</v>
+        <v>748.6266462815154</v>
       </c>
       <c r="O81" t="n">
-        <v>134.6287422742283</v>
+        <v>134.6287422742281</v>
       </c>
       <c r="P81" t="n">
         <v>1</v>
@@ -4793,10 +4793,10 @@
         <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>560.1529836120334</v>
+        <v>560.1529836120332</v>
       </c>
       <c r="N82" t="n">
-        <v>713.2107243963361</v>
+        <v>713.2107243963355</v>
       </c>
       <c r="O82" t="n">
         <v>129.9228670920045</v>
@@ -4846,13 +4846,13 @@
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>580.6867477823192</v>
+        <v>580.6867477823197</v>
       </c>
       <c r="N83" t="n">
-        <v>741.1624007055664</v>
+        <v>741.1624007055675</v>
       </c>
       <c r="O83" t="n">
-        <v>133.6417544411514</v>
+        <v>133.6417544411515</v>
       </c>
       <c r="P83" t="n">
         <v>0</v>
@@ -4899,13 +4899,13 @@
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>654.5129184760948</v>
+        <v>654.5129184760951</v>
       </c>
       <c r="N84" t="n">
-        <v>841.606199104045</v>
+        <v>841.6061991040459</v>
       </c>
       <c r="O84" t="n">
-        <v>146.7351021047658</v>
+        <v>146.7351021047659</v>
       </c>
       <c r="P84" t="n">
         <v>1</v>
@@ -4952,13 +4952,13 @@
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>568.366204871932</v>
+        <v>568.3662048719326</v>
       </c>
       <c r="N85" t="n">
-        <v>724.3896266154193</v>
+        <v>724.3896266154208</v>
       </c>
       <c r="O85" t="n">
-        <v>131.4144654900774</v>
+        <v>131.4144654900776</v>
       </c>
       <c r="P85" t="n">
         <v>0</v>
@@ -5005,13 +5005,13 @@
         <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>609.419123158934</v>
+        <v>609.4191231589333</v>
       </c>
       <c r="N86" t="n">
-        <v>780.2702920095406</v>
+        <v>780.2702920095387</v>
       </c>
       <c r="O86" t="n">
-        <v>138.7878843236739</v>
+        <v>138.7878843236737</v>
       </c>
       <c r="P86" t="n">
         <v>1</v>
@@ -5058,13 +5058,13 @@
         <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>641.1156665698751</v>
+        <v>641.1156665698754</v>
       </c>
       <c r="N87" t="n">
-        <v>823.386130352233</v>
+        <v>823.386130352234</v>
       </c>
       <c r="O87" t="n">
-        <v>144.3895859420567</v>
+        <v>144.3895859420568</v>
       </c>
       <c r="P87" t="n">
         <v>1</v>
@@ -5111,13 +5111,13 @@
         <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>652.7109414214515</v>
+        <v>652.7109414214514</v>
       </c>
       <c r="N88" t="n">
-        <v>839.4546973258241</v>
+        <v>839.4546973258238</v>
       </c>
       <c r="O88" t="n">
-        <v>146.446452222154</v>
+        <v>146.4464522221539</v>
       </c>
       <c r="P88" t="n">
         <v>1</v>
@@ -5164,13 +5164,13 @@
         <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>640.416979453585</v>
+        <v>640.4169794535854</v>
       </c>
       <c r="N89" t="n">
-        <v>822.7346159295963</v>
+        <v>822.7346159295972</v>
       </c>
       <c r="O89" t="n">
-        <v>144.2931102026527</v>
+        <v>144.2931102026528</v>
       </c>
       <c r="P89" t="n">
         <v>1</v>
@@ -5217,13 +5217,13 @@
         <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>588.1208850067926</v>
+        <v>588.1208850067918</v>
       </c>
       <c r="N90" t="n">
-        <v>751.5794614076001</v>
+        <v>751.5794614075982</v>
       </c>
       <c r="O90" t="n">
-        <v>135.0063208853083</v>
+        <v>135.0063208853081</v>
       </c>
       <c r="P90" t="n">
         <v>1</v>
@@ -5323,13 +5323,13 @@
         <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>588.1208360952041</v>
+        <v>588.1208360952033</v>
       </c>
       <c r="N92" t="n">
-        <v>751.5793363960771</v>
+        <v>751.5793363960747</v>
       </c>
       <c r="O92" t="n">
-        <v>135.0063068504098</v>
+        <v>135.0063068504095</v>
       </c>
       <c r="P92" t="n">
         <v>0</v>
@@ -5429,10 +5429,10 @@
         <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>588.1208419646026</v>
+        <v>588.1208419646025</v>
       </c>
       <c r="N94" t="n">
-        <v>751.5793513974792</v>
+        <v>751.5793513974791</v>
       </c>
       <c r="O94" t="n">
         <v>135.0063085345998</v>
@@ -5482,13 +5482,13 @@
         <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>648.6134969358343</v>
+        <v>648.6134969358346</v>
       </c>
       <c r="N95" t="n">
-        <v>833.8825082554021</v>
+        <v>833.8825082554031</v>
       </c>
       <c r="O95" t="n">
-        <v>145.7299874270371</v>
+        <v>145.7299874270373</v>
       </c>
       <c r="P95" t="n">
         <v>1</v>
@@ -5535,10 +5535,10 @@
         <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>648.6134285850812</v>
+        <v>648.613428585081</v>
       </c>
       <c r="N96" t="n">
-        <v>833.8823325066868</v>
+        <v>833.8823325066863</v>
       </c>
       <c r="O96" t="n">
         <v>145.7299682307933</v>
@@ -5591,10 +5591,10 @@
         <v>12260.92132165564</v>
       </c>
       <c r="N97" t="n">
-        <v>653.3153941455541</v>
+        <v>653.3153941455548</v>
       </c>
       <c r="O97" t="n">
-        <v>268.9628030544541</v>
+        <v>268.9628030544543</v>
       </c>
       <c r="P97" t="n">
         <v>1</v>
@@ -5644,7 +5644,7 @@
         <v>11913.20151857736</v>
       </c>
       <c r="N98" t="n">
-        <v>633.5553755331919</v>
+        <v>633.5553755331915</v>
       </c>
       <c r="O98" t="n">
         <v>262.9658860354789</v>
@@ -5697,10 +5697,10 @@
         <v>12338.16745614399</v>
       </c>
       <c r="N99" t="n">
-        <v>657.7044980978172</v>
+        <v>657.7044980978176</v>
       </c>
       <c r="O99" t="n">
-        <v>270.288813039666</v>
+        <v>270.2888130396661</v>
       </c>
       <c r="P99" t="n">
         <v>1</v>
@@ -5747,10 +5747,10 @@
         <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>12376.78720473022</v>
+        <v>12376.78720473021</v>
       </c>
       <c r="N100" t="n">
-        <v>659.8987804907094</v>
+        <v>659.8987804907091</v>
       </c>
       <c r="O100" t="n">
         <v>270.9509287015233</v>
@@ -5800,10 +5800,10 @@
         <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>12376.78720473022</v>
+        <v>12376.78720473021</v>
       </c>
       <c r="N101" t="n">
-        <v>659.8987804907094</v>
+        <v>659.8987804907091</v>
       </c>
       <c r="O101" t="n">
         <v>270.9509287015233</v>
@@ -5853,10 +5853,10 @@
         <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>12376.78720473022</v>
+        <v>12376.78720473021</v>
       </c>
       <c r="N102" t="n">
-        <v>659.8987804907094</v>
+        <v>659.8987804907091</v>
       </c>
       <c r="O102" t="n">
         <v>270.9509287015233</v>
@@ -5906,10 +5906,10 @@
         <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>12376.78720473022</v>
+        <v>12376.78720473021</v>
       </c>
       <c r="N103" t="n">
-        <v>659.8987804907094</v>
+        <v>659.8987804907091</v>
       </c>
       <c r="O103" t="n">
         <v>270.9509287015233</v>
@@ -5959,10 +5959,10 @@
         <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>12376.78720473022</v>
+        <v>12376.78720473021</v>
       </c>
       <c r="N104" t="n">
-        <v>659.8987804907094</v>
+        <v>659.8987804907091</v>
       </c>
       <c r="O104" t="n">
         <v>270.9509287015233</v>
@@ -6015,10 +6015,10 @@
         <v>10261.95414113973</v>
       </c>
       <c r="N105" t="n">
-        <v>539.6608137160758</v>
+        <v>539.6608137160757</v>
       </c>
       <c r="O105" t="n">
-        <v>233.8126258596797</v>
+        <v>233.8126258596796</v>
       </c>
       <c r="P105" t="n">
         <v>1</v>
@@ -6065,13 +6065,13 @@
         <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>5698.240079860588</v>
+        <v>5698.24007986059</v>
       </c>
       <c r="N106" t="n">
-        <v>609.9610483070097</v>
+        <v>609.9610483070101</v>
       </c>
       <c r="O106" t="n">
-        <v>214.5785157113777</v>
+        <v>214.5785157113778</v>
       </c>
       <c r="P106" t="n">
         <v>1</v>
@@ -6118,13 +6118,13 @@
         <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>5156.593270034833</v>
+        <v>5156.593270034834</v>
       </c>
       <c r="N107" t="n">
-        <v>547.6137165928614</v>
+        <v>547.6137165928616</v>
       </c>
       <c r="O107" t="n">
-        <v>198.3023579335267</v>
+        <v>198.3023579335268</v>
       </c>
       <c r="P107" t="n">
         <v>1</v>
@@ -6171,13 +6171,13 @@
         <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>5781.571371427434</v>
+        <v>5781.571371427431</v>
       </c>
       <c r="N108" t="n">
-        <v>619.5592633439464</v>
+        <v>619.5592633439458</v>
       </c>
       <c r="O108" t="n">
-        <v>217.0465565651391</v>
+        <v>217.046556565139</v>
       </c>
       <c r="P108" t="n">
         <v>1</v>
@@ -6277,10 +6277,10 @@
         <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>5823.152090834763</v>
+        <v>5823.152090834765</v>
       </c>
       <c r="N110" t="n">
-        <v>624.3407052354239</v>
+        <v>624.3407052354241</v>
       </c>
       <c r="O110" t="n">
         <v>218.2731714295742</v>
@@ -6330,13 +6330,13 @@
         <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>5927.187326696543</v>
+        <v>5927.187326696542</v>
       </c>
       <c r="N111" t="n">
-        <v>636.3136766622506</v>
+        <v>636.3136766622503</v>
       </c>
       <c r="O111" t="n">
-        <v>221.3338264543996</v>
+        <v>221.3338264543995</v>
       </c>
       <c r="P111" t="n">
         <v>1</v>
@@ -6383,13 +6383,13 @@
         <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>6680.259525789513</v>
+        <v>6680.259525789508</v>
       </c>
       <c r="N112" t="n">
-        <v>722.9170223210936</v>
+        <v>722.9170223210923</v>
       </c>
       <c r="O112" t="n">
-        <v>243.076267648921</v>
+        <v>243.0762676489208</v>
       </c>
       <c r="P112" t="n">
         <v>1</v>
@@ -6436,10 +6436,10 @@
         <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>5979.170676712378</v>
+        <v>5979.170676712379</v>
       </c>
       <c r="N113" t="n">
-        <v>642.2935708536238</v>
+        <v>642.293570853624</v>
       </c>
       <c r="O113" t="n">
         <v>222.8573823751524</v>
@@ -6489,13 +6489,13 @@
         <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>5979.148994634452</v>
+        <v>5979.148994634453</v>
       </c>
       <c r="N114" t="n">
-        <v>642.2889126042587</v>
+        <v>642.2889126042589</v>
       </c>
       <c r="O114" t="n">
-        <v>222.8563721997447</v>
+        <v>222.8563721997448</v>
       </c>
       <c r="P114" t="n">
         <v>1</v>
@@ -6595,10 +6595,10 @@
         <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>1924.052499896942</v>
+        <v>1924.052499896943</v>
       </c>
       <c r="N116" t="n">
-        <v>719.6605351006622</v>
+        <v>719.6605351006627</v>
       </c>
       <c r="O116" t="n">
         <v>177.6716244937601</v>
@@ -6648,13 +6648,13 @@
         <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>1963.969856401695</v>
+        <v>1963.969856401696</v>
       </c>
       <c r="N117" t="n">
-        <v>735.5938644040979</v>
+        <v>735.593864404099</v>
       </c>
       <c r="O117" t="n">
-        <v>180.5521870762426</v>
+        <v>180.5521870762428</v>
       </c>
       <c r="P117" t="n">
         <v>1</v>
@@ -6701,13 +6701,13 @@
         <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>1944.031239808219</v>
+        <v>1944.03123980822</v>
       </c>
       <c r="N118" t="n">
-        <v>727.6418790932976</v>
+        <v>727.6418790932981</v>
       </c>
       <c r="O118" t="n">
-        <v>179.1161118516317</v>
+        <v>179.1161118516318</v>
       </c>
       <c r="P118" t="n">
         <v>1</v>
@@ -6754,10 +6754,10 @@
         <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>1910.769991147872</v>
+        <v>1910.769991147873</v>
       </c>
       <c r="N119" t="n">
-        <v>714.3674415334888</v>
+        <v>714.3674415334889</v>
       </c>
       <c r="O119" t="n">
         <v>176.7107333999207</v>
@@ -6807,13 +6807,13 @@
         <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>2096.79823301517</v>
+        <v>2096.798233015169</v>
       </c>
       <c r="N120" t="n">
-        <v>788.5505729504121</v>
+        <v>788.5505729504114</v>
       </c>
       <c r="O120" t="n">
-        <v>190.0220225470723</v>
+        <v>190.0220225470722</v>
       </c>
       <c r="P120" t="n">
         <v>1</v>
@@ -6913,13 +6913,13 @@
         <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>2036.288020501128</v>
+        <v>2036.288020501129</v>
       </c>
       <c r="N122" t="n">
-        <v>764.4230934974815</v>
+        <v>764.4230934974823</v>
       </c>
       <c r="O122" t="n">
-        <v>185.7277087158372</v>
+        <v>185.7277087158373</v>
       </c>
       <c r="P122" t="n">
         <v>1</v>
@@ -6966,13 +6966,13 @@
         <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>1475.236970119675</v>
+        <v>1475.236970119677</v>
       </c>
       <c r="N123" t="n">
-        <v>540.4667680686005</v>
+        <v>540.4667680686017</v>
       </c>
       <c r="O123" t="n">
-        <v>144.0787541858497</v>
+        <v>144.0787541858499</v>
       </c>
       <c r="P123" t="n">
         <v>1</v>
@@ -7072,13 +7072,13 @@
         <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>654.7628629531127</v>
+        <v>654.7628629531117</v>
       </c>
       <c r="N125" t="n">
-        <v>842.2491046307451</v>
+        <v>842.2491046307424</v>
       </c>
       <c r="O125" t="n">
-        <v>146.8051491921837</v>
+        <v>146.8051491921834</v>
       </c>
       <c r="P125" t="n">
         <v>1</v>
@@ -7125,13 +7125,13 @@
         <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>658.8590869859648</v>
+        <v>658.8590869859655</v>
       </c>
       <c r="N126" t="n">
-        <v>847.8184813887863</v>
+        <v>847.8184813887884</v>
       </c>
       <c r="O126" t="n">
-        <v>147.5195485777278</v>
+        <v>147.519548577728</v>
       </c>
       <c r="P126" t="n">
         <v>1</v>
@@ -7178,13 +7178,13 @@
         <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>660.9074107914636</v>
+        <v>660.9074107914637</v>
       </c>
       <c r="N127" t="n">
-        <v>850.6037939622614</v>
+        <v>850.6037939622619</v>
       </c>
       <c r="O127" t="n">
-        <v>147.8763808888095</v>
+        <v>147.8763808888096</v>
       </c>
       <c r="P127" t="n">
         <v>1</v>
@@ -7231,13 +7231,13 @@
         <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>628.1231605015439</v>
+        <v>628.1231605015446</v>
       </c>
       <c r="N128" t="n">
-        <v>806.0169830202022</v>
+        <v>806.0169830202043</v>
       </c>
       <c r="O128" t="n">
-        <v>142.1291956084214</v>
+        <v>142.1291956084216</v>
       </c>
       <c r="P128" t="n">
         <v>1</v>
@@ -7284,13 +7284,13 @@
         <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>652.7140993663205</v>
+        <v>652.7140993663209</v>
       </c>
       <c r="N129" t="n">
-        <v>839.4628202418008</v>
+        <v>839.4628202418015</v>
       </c>
       <c r="O129" t="n">
-        <v>146.4473378938823</v>
+        <v>146.4473378938824</v>
       </c>
       <c r="P129" t="n">
         <v>1</v>
@@ -7337,13 +7337,13 @@
         <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>641.1033461089394</v>
+        <v>641.1033461089399</v>
       </c>
       <c r="N130" t="n">
-        <v>823.6721119558606</v>
+        <v>823.672111955862</v>
       </c>
       <c r="O130" t="n">
-        <v>144.4139649182598</v>
+        <v>144.4139649182599</v>
       </c>
       <c r="P130" t="n">
         <v>1</v>
@@ -7390,13 +7390,13 @@
         <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>658.8593303062838</v>
+        <v>658.8593303062846</v>
       </c>
       <c r="N131" t="n">
-        <v>847.8191075970472</v>
+        <v>847.8191075970492</v>
       </c>
       <c r="O131" t="n">
-        <v>147.5196166774664</v>
+        <v>147.5196166774666</v>
       </c>
       <c r="P131" t="n">
         <v>1</v>
@@ -7443,13 +7443,13 @@
         <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>654.7621190056168</v>
+        <v>654.7621190056152</v>
       </c>
       <c r="N132" t="n">
-        <v>842.2471906897084</v>
+        <v>842.2471906897043</v>
       </c>
       <c r="O132" t="n">
-        <v>146.8049406905379</v>
+        <v>146.8049406905375</v>
       </c>
       <c r="P132" t="n">
         <v>1</v>
@@ -7496,10 +7496,10 @@
         <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>598.5207106294342</v>
+        <v>598.5207106294345</v>
       </c>
       <c r="N133" t="n">
-        <v>764.6733418073951</v>
+        <v>764.6733418073956</v>
       </c>
       <c r="O133" t="n">
         <v>136.7753298246918</v>
@@ -7552,7 +7552,7 @@
         <v>598.5706365056182</v>
       </c>
       <c r="N134" t="n">
-        <v>764.8009182744461</v>
+        <v>764.8009182744463</v>
       </c>
       <c r="O134" t="n">
         <v>136.7895914435061</v>
@@ -7602,10 +7602,10 @@
         <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>596.5198831335207</v>
+        <v>596.5198831335209</v>
       </c>
       <c r="N135" t="n">
-        <v>762.0116961153464</v>
+        <v>762.0116961153468</v>
       </c>
       <c r="O135" t="n">
         <v>136.4228285165048</v>
@@ -7655,13 +7655,13 @@
         <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>598.8272146781213</v>
+        <v>598.8272146781209</v>
       </c>
       <c r="N136" t="n">
-        <v>765.4567248488701</v>
+        <v>765.4567248488689</v>
       </c>
       <c r="O136" t="n">
-        <v>136.8628891915232</v>
+        <v>136.8628891915231</v>
       </c>
       <c r="P136" t="n">
         <v>0</v>
@@ -7708,13 +7708,13 @@
         <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>640.4890754181864</v>
+        <v>640.4890754181862</v>
       </c>
       <c r="N137" t="n">
-        <v>821.7774523194472</v>
+        <v>821.7774523194466</v>
       </c>
       <c r="O137" t="n">
-        <v>144.2132094588075</v>
+        <v>144.2132094588074</v>
       </c>
       <c r="P137" t="n">
         <v>1</v>
@@ -7761,13 +7761,13 @@
         <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>596.4852214122478</v>
+        <v>596.4852214122465</v>
       </c>
       <c r="N138" t="n">
-        <v>761.9231429241103</v>
+        <v>761.9231429241069</v>
       </c>
       <c r="O138" t="n">
-        <v>136.4129197610618</v>
+        <v>136.4129197610614</v>
       </c>
       <c r="P138" t="n">
         <v>1</v>
@@ -7817,7 +7817,7 @@
         <v>550.6948909466378</v>
       </c>
       <c r="N139" t="n">
-        <v>699.6770607557107</v>
+        <v>699.6770607557106</v>
       </c>
       <c r="O139" t="n">
         <v>128.1375982826837</v>
@@ -7867,13 +7867,13 @@
         <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>606.862082405034</v>
+        <v>606.8620824050338</v>
       </c>
       <c r="N140" t="n">
-        <v>776.1847426014191</v>
+        <v>776.1847426014186</v>
       </c>
       <c r="O140" t="n">
-        <v>138.2786247292433</v>
+        <v>138.2786247292432</v>
       </c>
       <c r="P140" t="n">
         <v>0</v>
@@ -7973,10 +7973,10 @@
         <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>638.5421321573408</v>
+        <v>638.5421321573406</v>
       </c>
       <c r="N142" t="n">
-        <v>819.1581596101851</v>
+        <v>819.1581596101845</v>
       </c>
       <c r="O142" t="n">
         <v>143.8736528993178</v>
@@ -8026,13 +8026,13 @@
         <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>645.7119279963997</v>
+        <v>645.7119279963995</v>
       </c>
       <c r="N143" t="n">
-        <v>828.9054388114198</v>
+        <v>828.9054388114196</v>
       </c>
       <c r="O143" t="n">
-        <v>145.1316714216078</v>
+        <v>145.1316714216077</v>
       </c>
       <c r="P143" t="n">
         <v>1</v>
@@ -8079,13 +8079,13 @@
         <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>638.3682668804166</v>
+        <v>638.368266880415</v>
       </c>
       <c r="N144" t="n">
-        <v>819.9488570872315</v>
+        <v>819.9488570872275</v>
       </c>
       <c r="O144" t="n">
-        <v>143.9332742414114</v>
+        <v>143.9332742414109</v>
       </c>
       <c r="P144" t="n">
         <v>1</v>
@@ -8132,13 +8132,13 @@
         <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>652.7116273455169</v>
+        <v>652.7116273455157</v>
       </c>
       <c r="N145" t="n">
-        <v>839.4564616672648</v>
+        <v>839.4564616672615</v>
       </c>
       <c r="O145" t="n">
-        <v>146.446644595134</v>
+        <v>146.4466445951336</v>
       </c>
       <c r="P145" t="n">
         <v>1</v>
@@ -8185,13 +8185,13 @@
         <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>646.5650144004403</v>
+        <v>646.5650144004395</v>
       </c>
       <c r="N146" t="n">
-        <v>831.0971129704305</v>
+        <v>831.0971129704283</v>
       </c>
       <c r="O146" t="n">
-        <v>145.3713880237198</v>
+        <v>145.3713880237195</v>
       </c>
       <c r="P146" t="n">
         <v>0</v>
@@ -8238,13 +8238,13 @@
         <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>660.9053773596444</v>
+        <v>660.9053773596438</v>
       </c>
       <c r="N147" t="n">
-        <v>850.5985598186245</v>
+        <v>850.5985598186232</v>
       </c>
       <c r="O147" t="n">
-        <v>147.8758121699208</v>
+        <v>147.8758121699207</v>
       </c>
       <c r="P147" t="n">
         <v>1</v>
@@ -8291,13 +8291,13 @@
         <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>654.7601353515979</v>
+        <v>654.7601353515977</v>
       </c>
       <c r="N148" t="n">
-        <v>842.2420873874694</v>
+        <v>842.242087387469</v>
       </c>
       <c r="O148" t="n">
-        <v>146.8043847441647</v>
+        <v>146.8043847441646</v>
       </c>
       <c r="P148" t="n">
         <v>1</v>
@@ -8344,13 +8344,13 @@
         <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>557.3200618782346</v>
+        <v>557.3200618782341</v>
       </c>
       <c r="N149" t="n">
-        <v>709.6479824896156</v>
+        <v>709.6479824896145</v>
       </c>
       <c r="O149" t="n">
-        <v>129.4337862067077</v>
+        <v>129.4337862067075</v>
       </c>
       <c r="P149" t="n">
         <v>1</v>
@@ -8397,10 +8397,10 @@
         <v>0</v>
       </c>
       <c r="M150" t="n">
-        <v>570.6715371213645</v>
+        <v>570.6715371213644</v>
       </c>
       <c r="N150" t="n">
-        <v>727.8272949627939</v>
+        <v>727.8272949627935</v>
       </c>
       <c r="O150" t="n">
         <v>131.8592867596268</v>
@@ -8450,13 +8450,13 @@
         <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>636.3187843304257</v>
+        <v>636.3187843304253</v>
       </c>
       <c r="N151" t="n">
-        <v>817.1611786859554</v>
+        <v>817.161178685954</v>
       </c>
       <c r="O151" t="n">
-        <v>143.5729252506848</v>
+        <v>143.5729252506846</v>
       </c>
       <c r="P151" t="n">
         <v>1</v>
@@ -8503,13 +8503,13 @@
         <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>639.392999253478</v>
+        <v>639.3929992534778</v>
       </c>
       <c r="N152" t="n">
-        <v>821.3426955004646</v>
+        <v>821.3426955004638</v>
       </c>
       <c r="O152" t="n">
-        <v>144.1133350883858</v>
+        <v>144.1133350883857</v>
       </c>
       <c r="P152" t="n">
         <v>1</v>
@@ -8556,13 +8556,13 @@
         <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>625.208737237033</v>
+        <v>625.2087372370339</v>
       </c>
       <c r="N153" t="n">
-        <v>803.4840226924107</v>
+        <v>803.484022692413</v>
       </c>
       <c r="O153" t="n">
-        <v>141.7408008584142</v>
+        <v>141.7408008584145</v>
       </c>
       <c r="P153" t="n">
         <v>0</v>
@@ -8662,13 +8662,13 @@
         <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>631.4238777318945</v>
+        <v>631.4238777318938</v>
       </c>
       <c r="N155" t="n">
-        <v>812.0194419693316</v>
+        <v>812.0194419693294</v>
       </c>
       <c r="O155" t="n">
-        <v>142.8444805326068</v>
+        <v>142.8444805326065</v>
       </c>
       <c r="P155" t="n">
         <v>1</v>
@@ -8715,13 +8715,13 @@
         <v>0</v>
       </c>
       <c r="M156" t="n">
-        <v>552.8033854150857</v>
+        <v>552.8033854150859</v>
       </c>
       <c r="N156" t="n">
-        <v>705.0451492421465</v>
+        <v>705.0451492421471</v>
       </c>
       <c r="O156" t="n">
-        <v>128.7511562723119</v>
+        <v>128.751156272312</v>
       </c>
       <c r="P156" t="n">
         <v>1</v>
@@ -8768,13 +8768,13 @@
         <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>662.0492624514311</v>
+        <v>662.0492624514321</v>
       </c>
       <c r="N157" t="n">
-        <v>853.5455142864752</v>
+        <v>853.5455142864779</v>
       </c>
       <c r="O157" t="n">
-        <v>148.1958078963705</v>
+        <v>148.1958078963708</v>
       </c>
       <c r="P157" t="n">
         <v>1</v>
@@ -8821,13 +8821,13 @@
         <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>604.7447060454454</v>
+        <v>604.7447060454451</v>
       </c>
       <c r="N158" t="n">
-        <v>775.68729926295</v>
+        <v>775.6872992629493</v>
       </c>
       <c r="O158" t="n">
-        <v>138.1135725149412</v>
+        <v>138.1135725149411</v>
       </c>
       <c r="P158" t="n">
         <v>1</v>
@@ -8874,13 +8874,13 @@
         <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>631.3933911831804</v>
+        <v>631.3933911831799</v>
       </c>
       <c r="N159" t="n">
-        <v>811.9410316541117</v>
+        <v>811.9410316541108</v>
       </c>
       <c r="O159" t="n">
-        <v>142.8358595232402</v>
+        <v>142.8358595232401</v>
       </c>
       <c r="P159" t="n">
         <v>1</v>
@@ -8927,13 +8927,13 @@
         <v>0</v>
       </c>
       <c r="M160" t="n">
-        <v>631.3513720581645</v>
+        <v>631.3513720581648</v>
       </c>
       <c r="N160" t="n">
-        <v>811.8329661692685</v>
+        <v>811.8329661692692</v>
       </c>
       <c r="O160" t="n">
-        <v>142.8239774937611</v>
+        <v>142.8239774937612</v>
       </c>
       <c r="P160" t="n">
         <v>1</v>
@@ -8980,13 +8980,13 @@
         <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>619.0855592708522</v>
+        <v>619.0855592708519</v>
       </c>
       <c r="N161" t="n">
-        <v>795.1855754708949</v>
+        <v>795.1855754708947</v>
       </c>
       <c r="O161" t="n">
-        <v>140.6604217251438</v>
+        <v>140.6604217251437</v>
       </c>
       <c r="P161" t="n">
         <v>0</v>
@@ -9033,13 +9033,13 @@
         <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>1254.883755660859</v>
+        <v>1254.88375566086</v>
       </c>
       <c r="N162" t="n">
-        <v>1154.87651821428</v>
+        <v>1154.876518214281</v>
       </c>
       <c r="O162" t="n">
-        <v>202.2640271183793</v>
+        <v>202.2640271183794</v>
       </c>
       <c r="P162" t="n">
         <v>1</v>
@@ -9089,10 +9089,10 @@
         <v>1328.017439258166</v>
       </c>
       <c r="N163" t="n">
-        <v>1228.7392116088</v>
+        <v>1228.739211608801</v>
       </c>
       <c r="O163" t="n">
-        <v>211.6073767630379</v>
+        <v>211.607376763038</v>
       </c>
       <c r="P163" t="n">
         <v>1</v>
@@ -9139,13 +9139,13 @@
         <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>1323.610803907402</v>
+        <v>1323.6108039074</v>
       </c>
       <c r="N164" t="n">
-        <v>1224.680589770133</v>
+        <v>1224.68058977013</v>
       </c>
       <c r="O164" t="n">
-        <v>211.0821422750111</v>
+        <v>211.0821422750107</v>
       </c>
       <c r="P164" t="n">
         <v>1</v>
@@ -9192,13 +9192,13 @@
         <v>0</v>
       </c>
       <c r="M165" t="n">
-        <v>1323.286675093924</v>
+        <v>1323.286675093923</v>
       </c>
       <c r="N165" t="n">
-        <v>1224.0808580941</v>
+        <v>1224.080858094097</v>
       </c>
       <c r="O165" t="n">
-        <v>211.0175314112063</v>
+        <v>211.017531411206</v>
       </c>
       <c r="P165" t="n">
         <v>1</v>
@@ -9354,10 +9354,10 @@
         <v>1469.243390549787</v>
       </c>
       <c r="N168" t="n">
-        <v>1371.402729874885</v>
+        <v>1371.402729874886</v>
       </c>
       <c r="O168" t="n">
-        <v>229.2745983122634</v>
+        <v>229.2745983122635</v>
       </c>
       <c r="P168" t="n">
         <v>1</v>
@@ -9404,13 +9404,13 @@
         <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>1464.377154112812</v>
+        <v>1464.377154112811</v>
       </c>
       <c r="N169" t="n">
-        <v>1366.486866708644</v>
+        <v>1366.486866708643</v>
       </c>
       <c r="O169" t="n">
-        <v>228.6735675243734</v>
+        <v>228.6735675243733</v>
       </c>
       <c r="P169" t="n">
         <v>1</v>
@@ -9460,10 +9460,10 @@
         <v>1359.74559229671</v>
       </c>
       <c r="N170" t="n">
-        <v>1260.83500189583</v>
+        <v>1260.835001895832</v>
       </c>
       <c r="O170" t="n">
-        <v>215.6222349693863</v>
+        <v>215.6222349693864</v>
       </c>
       <c r="P170" t="n">
         <v>1</v>
@@ -9510,13 +9510,13 @@
         <v>0</v>
       </c>
       <c r="M171" t="n">
-        <v>1355.597344936382</v>
+        <v>1355.597344936383</v>
       </c>
       <c r="N171" t="n">
-        <v>1256.570195044777</v>
+        <v>1256.570195044778</v>
       </c>
       <c r="O171" t="n">
-        <v>215.0928898775021</v>
+        <v>215.0928898775023</v>
       </c>
       <c r="P171" t="n">
         <v>1</v>
@@ -9566,10 +9566,10 @@
         <v>12145.03532589695</v>
       </c>
       <c r="N172" t="n">
-        <v>646.7303786446438</v>
+        <v>646.7303786446431</v>
       </c>
       <c r="O172" t="n">
-        <v>266.969302167332</v>
+        <v>266.9693021673319</v>
       </c>
       <c r="P172" t="n">
         <v>1</v>
@@ -9619,7 +9619,7 @@
         <v>12183.66624837616</v>
       </c>
       <c r="N173" t="n">
-        <v>648.9255661281769</v>
+        <v>648.9255661281766</v>
       </c>
       <c r="O173" t="n">
         <v>267.6344041068228</v>
@@ -9672,10 +9672,10 @@
         <v>11835.90485414048</v>
       </c>
       <c r="N174" t="n">
-        <v>629.1622113853601</v>
+        <v>629.1622113853599</v>
       </c>
       <c r="O174" t="n">
-        <v>261.6264699517707</v>
+        <v>261.6264699517706</v>
       </c>
       <c r="P174" t="n">
         <v>1</v>
@@ -9725,10 +9725,10 @@
         <v>11835.90485414048</v>
       </c>
       <c r="N175" t="n">
-        <v>629.1622113853601</v>
+        <v>629.1622113853599</v>
       </c>
       <c r="O175" t="n">
-        <v>261.6264699517707</v>
+        <v>261.6264699517706</v>
       </c>
       <c r="P175" t="n">
         <v>1</v>
@@ -9778,10 +9778,10 @@
         <v>12338.16745614399</v>
       </c>
       <c r="N176" t="n">
-        <v>657.7044980978172</v>
+        <v>657.7044980978176</v>
       </c>
       <c r="O176" t="n">
-        <v>270.288813039666</v>
+        <v>270.2888130396661</v>
       </c>
       <c r="P176" t="n">
         <v>1</v>
@@ -9828,13 +9828,13 @@
         <v>0</v>
       </c>
       <c r="M177" t="n">
-        <v>12608.4600581924</v>
+        <v>12608.46005819238</v>
       </c>
       <c r="N177" t="n">
-        <v>673.0607491592607</v>
+        <v>673.0607491592594</v>
       </c>
       <c r="O177" t="n">
-        <v>274.9113332401161</v>
+        <v>274.9113332401157</v>
       </c>
       <c r="P177" t="n">
         <v>1</v>
@@ -9881,13 +9881,13 @@
         <v>0</v>
       </c>
       <c r="M178" t="n">
-        <v>12608.4600581924</v>
+        <v>12608.46005819238</v>
       </c>
       <c r="N178" t="n">
-        <v>673.0607491592607</v>
+        <v>673.0607491592594</v>
       </c>
       <c r="O178" t="n">
-        <v>274.9113332401161</v>
+        <v>274.9113332401157</v>
       </c>
       <c r="P178" t="n">
         <v>1</v>
@@ -9987,10 +9987,10 @@
         <v>0</v>
       </c>
       <c r="M180" t="n">
-        <v>500.2684787621819</v>
+        <v>500.2684787621818</v>
       </c>
       <c r="N180" t="n">
-        <v>631.3563171057508</v>
+        <v>631.3563171057502</v>
       </c>
       <c r="O180" t="n">
         <v>118.8332705353729</v>
@@ -10040,13 +10040,13 @@
         <v>0</v>
       </c>
       <c r="M181" t="n">
-        <v>520.8433970695098</v>
+        <v>520.84339706951</v>
       </c>
       <c r="N181" t="n">
-        <v>659.3802593444574</v>
+        <v>659.3802593444577</v>
       </c>
       <c r="O181" t="n">
-        <v>122.6718065967749</v>
+        <v>122.671806596775</v>
       </c>
       <c r="P181" t="n">
         <v>1</v>
@@ -10093,13 +10093,13 @@
         <v>0</v>
       </c>
       <c r="M182" t="n">
-        <v>553.7903286163931</v>
+        <v>553.790328616393</v>
       </c>
       <c r="N182" t="n">
-        <v>704.3117183146014</v>
+        <v>704.3117183146011</v>
       </c>
       <c r="O182" t="n">
-        <v>128.741569354119</v>
+        <v>128.7415693541189</v>
       </c>
       <c r="P182" t="n">
         <v>1</v>
@@ -10146,10 +10146,10 @@
         <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>547.5818833483249</v>
+        <v>547.5818833483251</v>
       </c>
       <c r="N183" t="n">
-        <v>695.8064075206677</v>
+        <v>695.8064075206679</v>
       </c>
       <c r="O183" t="n">
         <v>127.6017056581843</v>
@@ -10252,13 +10252,13 @@
         <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>617.3848951277234</v>
+        <v>617.384895127723</v>
       </c>
       <c r="N185" t="n">
-        <v>790.8227338838382</v>
+        <v>790.822733883837</v>
       </c>
       <c r="O185" t="n">
-        <v>140.1775847146955</v>
+        <v>140.1775847146953</v>
       </c>
       <c r="P185" t="n">
         <v>1</v>
@@ -10305,13 +10305,13 @@
         <v>0</v>
       </c>
       <c r="M186" t="n">
-        <v>633.7896901936296</v>
+        <v>633.7896901936309</v>
       </c>
       <c r="N186" t="n">
-        <v>813.1424253942797</v>
+        <v>813.1424253942832</v>
       </c>
       <c r="O186" t="n">
-        <v>143.0769267207006</v>
+        <v>143.076926720701</v>
       </c>
       <c r="P186" t="n">
         <v>1</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="M187" t="n">
-        <v>632.2398518669805</v>
+        <v>632.2398518669806</v>
       </c>
       <c r="N187" t="n">
-        <v>811.6374333805453</v>
+        <v>811.6374333805456</v>
       </c>
       <c r="O187" t="n">
         <v>142.8569919483925</v>
@@ -10411,13 +10411,13 @@
         <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>634.2892234140028</v>
+        <v>634.2892234140025</v>
       </c>
       <c r="N188" t="n">
-        <v>814.4247174051735</v>
+        <v>814.4247174051732</v>
       </c>
       <c r="O188" t="n">
-        <v>143.217901556582</v>
+        <v>143.2179015565819</v>
       </c>
       <c r="P188" t="n">
         <v>0</v>
@@ -10570,13 +10570,13 @@
         <v>0</v>
       </c>
       <c r="M191" t="n">
-        <v>611.7360662331355</v>
+        <v>611.7360662331358</v>
       </c>
       <c r="N191" t="n">
-        <v>783.7421975131163</v>
+        <v>783.7421975131172</v>
       </c>
       <c r="O191" t="n">
-        <v>139.228337277381</v>
+        <v>139.2283372773811</v>
       </c>
       <c r="P191" t="n">
         <v>0</v>
@@ -10626,7 +10626,7 @@
         <v>615.8376932752116</v>
       </c>
       <c r="N192" t="n">
-        <v>789.3229565370548</v>
+        <v>789.3229565370547</v>
       </c>
       <c r="O192" t="n">
         <v>139.9567773116729</v>
@@ -10676,13 +10676,13 @@
         <v>0</v>
       </c>
       <c r="M193" t="n">
-        <v>632.2395058551227</v>
+        <v>632.2395058551236</v>
       </c>
       <c r="N193" t="n">
-        <v>811.6365449958651</v>
+        <v>811.6365449958674</v>
       </c>
       <c r="O193" t="n">
-        <v>142.856894220035</v>
+        <v>142.8568942200353</v>
       </c>
       <c r="P193" t="n">
         <v>1</v>
@@ -10729,10 +10729,10 @@
         <v>0</v>
       </c>
       <c r="M194" t="n">
-        <v>605.5826852273315</v>
+        <v>605.5826852273316</v>
       </c>
       <c r="N194" t="n">
-        <v>775.3691599913432</v>
+        <v>775.3691599913435</v>
       </c>
       <c r="O194" t="n">
         <v>138.133057216484</v>
@@ -10782,10 +10782,10 @@
         <v>0</v>
       </c>
       <c r="M195" t="n">
-        <v>634.3073712003162</v>
+        <v>634.3073712003161</v>
       </c>
       <c r="N195" t="n">
-        <v>814.4713214357365</v>
+        <v>814.4713214357361</v>
       </c>
       <c r="O195" t="n">
         <v>143.2230236228908</v>
@@ -10835,13 +10835,13 @@
         <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>632.2507931706327</v>
+        <v>632.2507931706322</v>
       </c>
       <c r="N196" t="n">
-        <v>811.6655254042546</v>
+        <v>811.6655254042532</v>
       </c>
       <c r="O196" t="n">
-        <v>142.8600822413887</v>
+        <v>142.8600822413885</v>
       </c>
       <c r="P196" t="n">
         <v>1</v>
@@ -10888,13 +10888,13 @@
         <v>0</v>
       </c>
       <c r="M197" t="n">
-        <v>619.9442227398766</v>
+        <v>619.9442227398773</v>
       </c>
       <c r="N197" t="n">
-        <v>794.9165533564233</v>
+        <v>794.9165533564252</v>
       </c>
       <c r="O197" t="n">
-        <v>140.6853659847893</v>
+        <v>140.6853659847895</v>
       </c>
       <c r="P197" t="n">
         <v>1</v>
@@ -10941,13 +10941,13 @@
         <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>611.7417675479469</v>
+        <v>611.741767547948</v>
       </c>
       <c r="N198" t="n">
-        <v>783.756806368366</v>
+        <v>783.756806368369</v>
       </c>
       <c r="O198" t="n">
-        <v>139.229959270815</v>
+        <v>139.2299592708153</v>
       </c>
       <c r="P198" t="n">
         <v>1</v>
@@ -10994,13 +10994,13 @@
         <v>0</v>
       </c>
       <c r="M199" t="n">
-        <v>611.746188003729</v>
+        <v>611.7461880037296</v>
       </c>
       <c r="N199" t="n">
-        <v>783.7681332876897</v>
+        <v>783.7681332876912</v>
       </c>
       <c r="O199" t="n">
-        <v>139.2312168693375</v>
+        <v>139.2312168693376</v>
       </c>
       <c r="P199" t="n">
         <v>1</v>
@@ -11047,13 +11047,13 @@
         <v>0</v>
       </c>
       <c r="M200" t="n">
-        <v>628.1527094792964</v>
+        <v>628.1527094792973</v>
       </c>
       <c r="N200" t="n">
-        <v>806.0928201795737</v>
+        <v>806.0928201795759</v>
       </c>
       <c r="O200" t="n">
-        <v>142.1375534381417</v>
+        <v>142.137553438142</v>
       </c>
       <c r="P200" t="n">
         <v>1</v>
@@ -11100,13 +11100,13 @@
         <v>0</v>
       </c>
       <c r="M201" t="n">
-        <v>6363.205635741176</v>
+        <v>6363.20563574116</v>
       </c>
       <c r="N201" t="n">
-        <v>175.965933209928</v>
+        <v>175.9659332099272</v>
       </c>
       <c r="O201" t="n">
-        <v>118.4767925020029</v>
+        <v>118.4767925020025</v>
       </c>
       <c r="P201" t="n">
         <v>0</v>
@@ -11153,10 +11153,10 @@
         <v>0</v>
       </c>
       <c r="M202" t="n">
-        <v>6305.711354196944</v>
+        <v>6305.711354196946</v>
       </c>
       <c r="N202" t="n">
-        <v>174.3387269954112</v>
+        <v>174.3387269954113</v>
       </c>
       <c r="O202" t="n">
         <v>117.6604369760613</v>
@@ -11206,13 +11206,13 @@
         <v>0</v>
       </c>
       <c r="M203" t="n">
-        <v>6133.199745562881</v>
+        <v>6133.199745562873</v>
       </c>
       <c r="N203" t="n">
-        <v>169.4556180489502</v>
+        <v>169.4556180489498</v>
       </c>
       <c r="O203" t="n">
-        <v>115.1992795777448</v>
+        <v>115.1992795777446</v>
       </c>
       <c r="P203" t="n">
         <v>1</v>
@@ -11259,13 +11259,13 @@
         <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>6209.877002917628</v>
+        <v>6209.877002917621</v>
       </c>
       <c r="N204" t="n">
-        <v>171.626169837138</v>
+        <v>171.6261698371376</v>
       </c>
       <c r="O204" t="n">
-        <v>116.2953914406448</v>
+        <v>116.2953914406447</v>
       </c>
       <c r="P204" t="n">
         <v>0</v>
@@ -11312,13 +11312,13 @@
         <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>6267.379215259171</v>
+        <v>6267.379215259175</v>
       </c>
       <c r="N205" t="n">
-        <v>173.2537871040545</v>
+        <v>173.2537871040547</v>
       </c>
       <c r="O205" t="n">
-        <v>117.1150913527903</v>
+        <v>117.1150913527904</v>
       </c>
       <c r="P205" t="n">
         <v>0</v>
@@ -11365,13 +11365,13 @@
         <v>0</v>
       </c>
       <c r="M206" t="n">
-        <v>6133.199745562881</v>
+        <v>6133.199745562873</v>
       </c>
       <c r="N206" t="n">
-        <v>169.4556180489502</v>
+        <v>169.4556180489498</v>
       </c>
       <c r="O206" t="n">
-        <v>115.1992795777448</v>
+        <v>115.1992795777446</v>
       </c>
       <c r="P206" t="n">
         <v>1</v>
@@ -11418,13 +11418,13 @@
         <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>6133.199745562881</v>
+        <v>6133.199745562873</v>
       </c>
       <c r="N207" t="n">
-        <v>169.4556180489502</v>
+        <v>169.4556180489498</v>
       </c>
       <c r="O207" t="n">
-        <v>115.1992795777448</v>
+        <v>115.1992795777446</v>
       </c>
       <c r="P207" t="n">
         <v>0</v>
@@ -11471,13 +11471,13 @@
         <v>0</v>
       </c>
       <c r="M208" t="n">
-        <v>6420.695295000781</v>
+        <v>6420.695295000791</v>
       </c>
       <c r="N208" t="n">
-        <v>177.5928995278671</v>
+        <v>177.5928995278677</v>
       </c>
       <c r="O208" t="n">
-        <v>119.2911743649034</v>
+        <v>119.2911743649037</v>
       </c>
       <c r="P208" t="n">
         <v>1</v>
@@ -11524,13 +11524,13 @@
         <v>0</v>
       </c>
       <c r="M209" t="n">
-        <v>6420.695295000781</v>
+        <v>6420.695295000791</v>
       </c>
       <c r="N209" t="n">
-        <v>177.5928995278671</v>
+        <v>177.5928995278677</v>
       </c>
       <c r="O209" t="n">
-        <v>119.2911743649034</v>
+        <v>119.2911743649037</v>
       </c>
       <c r="P209" t="n">
         <v>1</v>
@@ -11577,13 +11577,13 @@
         <v>0</v>
       </c>
       <c r="M210" t="n">
-        <v>287.9865597088102</v>
+        <v>287.9865597088108</v>
       </c>
       <c r="N210" t="n">
-        <v>190.466508131538</v>
+        <v>190.4665081315388</v>
       </c>
       <c r="O210" t="n">
-        <v>56.85286628065688</v>
+        <v>56.85286628065703</v>
       </c>
       <c r="P210" t="n">
         <v>0</v>
@@ -11630,13 +11630,13 @@
         <v>0</v>
       </c>
       <c r="M211" t="n">
-        <v>289.0063840341791</v>
+        <v>289.0063840341787</v>
       </c>
       <c r="N211" t="n">
-        <v>191.1586970659101</v>
+        <v>191.1586970659096</v>
       </c>
       <c r="O211" t="n">
-        <v>57.00643597850117</v>
+        <v>57.00643597850106</v>
       </c>
       <c r="P211" t="n">
         <v>0</v>
@@ -11683,13 +11683,13 @@
         <v>0</v>
       </c>
       <c r="M212" t="n">
-        <v>276.7770399532076</v>
+        <v>276.7770399532068</v>
       </c>
       <c r="N212" t="n">
-        <v>182.8639495948289</v>
+        <v>182.8639495948278</v>
       </c>
       <c r="O212" t="n">
-        <v>55.15648260695913</v>
+        <v>55.15648260695892</v>
       </c>
       <c r="P212" t="n">
         <v>0</v>
@@ -11736,13 +11736,13 @@
         <v>0</v>
       </c>
       <c r="M213" t="n">
-        <v>270.6687932365135</v>
+        <v>270.668793236513</v>
       </c>
       <c r="N213" t="n">
-        <v>178.7252464042265</v>
+        <v>178.725246404226</v>
       </c>
       <c r="O213" t="n">
-        <v>54.22536686123821</v>
+        <v>54.2253668612381</v>
       </c>
       <c r="P213" t="n">
         <v>0</v>
@@ -11789,13 +11789,13 @@
         <v>0</v>
       </c>
       <c r="M214" t="n">
-        <v>287.9862349418494</v>
+        <v>287.9862349418485</v>
       </c>
       <c r="N214" t="n">
-        <v>190.4660785476424</v>
+        <v>190.4660785476412</v>
       </c>
       <c r="O214" t="n">
-        <v>56.85278613833179</v>
+        <v>56.85278613833156</v>
       </c>
       <c r="P214" t="n">
         <v>0</v>
@@ -11842,13 +11842,13 @@
         <v>0</v>
       </c>
       <c r="M215" t="n">
-        <v>281.8718470628016</v>
+        <v>281.8718470628014</v>
       </c>
       <c r="N215" t="n">
-        <v>186.3190412924734</v>
+        <v>186.3190412924731</v>
       </c>
       <c r="O215" t="n">
-        <v>55.92957842112366</v>
+        <v>55.92957842112361</v>
       </c>
       <c r="P215" t="n">
         <v>0</v>
@@ -11895,13 +11895,13 @@
         <v>0</v>
       </c>
       <c r="M216" t="n">
-        <v>313.5222599475834</v>
+        <v>313.5222599475828</v>
       </c>
       <c r="N216" t="n">
-        <v>207.8252857836702</v>
+        <v>207.8252857836694</v>
       </c>
       <c r="O216" t="n">
-        <v>60.66193906116699</v>
+        <v>60.66193906116683</v>
       </c>
       <c r="P216" t="n">
         <v>0</v>
@@ -11948,13 +11948,13 @@
         <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>287.0481764436101</v>
+        <v>287.0481764436109</v>
       </c>
       <c r="N217" t="n">
-        <v>189.8820535469895</v>
+        <v>189.8820535469906</v>
       </c>
       <c r="O217" t="n">
-        <v>56.71927331005853</v>
+        <v>56.71927331005875</v>
       </c>
       <c r="P217" t="n">
         <v>0</v>
@@ -12001,13 +12001,13 @@
         <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>311.4864990099243</v>
+        <v>311.4864990099227</v>
       </c>
       <c r="N218" t="n">
-        <v>206.4459158398453</v>
+        <v>206.4459158398433</v>
       </c>
       <c r="O218" t="n">
-        <v>60.36190738334505</v>
+        <v>60.36190738334471</v>
       </c>
       <c r="P218" t="n">
         <v>0</v>
@@ -12054,13 +12054,13 @@
         <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>285.0107838973954</v>
+        <v>285.0107838973948</v>
       </c>
       <c r="N219" t="n">
-        <v>188.5006563487354</v>
+        <v>188.5006563487347</v>
       </c>
       <c r="O219" t="n">
-        <v>56.41203368002775</v>
+        <v>56.41203368002761</v>
       </c>
       <c r="P219" t="n">
         <v>0</v>
@@ -12107,13 +12107,13 @@
         <v>0</v>
       </c>
       <c r="M220" t="n">
-        <v>269.0461506505295</v>
+        <v>269.046150650529</v>
       </c>
       <c r="N220" t="n">
-        <v>177.6734738241429</v>
+        <v>177.6734738241422</v>
       </c>
       <c r="O220" t="n">
-        <v>53.98436440849039</v>
+        <v>53.98436440849026</v>
       </c>
       <c r="P220" t="n">
         <v>0</v>
@@ -12160,13 +12160,13 @@
         <v>0</v>
       </c>
       <c r="M221" t="n">
-        <v>288.7458801829952</v>
+        <v>288.7458801829954</v>
       </c>
       <c r="N221" t="n">
-        <v>191.0330637526654</v>
+        <v>191.0330637526657</v>
       </c>
       <c r="O221" t="n">
-        <v>56.97485381484663</v>
+        <v>56.97485381484667</v>
       </c>
       <c r="P221" t="n">
         <v>0</v>
@@ -12213,13 +12213,13 @@
         <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>286.3690670607328</v>
+        <v>286.3690670607324</v>
       </c>
       <c r="N222" t="n">
-        <v>189.4216148727348</v>
+        <v>189.4216148727342</v>
       </c>
       <c r="O222" t="n">
-        <v>56.616927014191</v>
+        <v>56.61692701419089</v>
       </c>
       <c r="P222" t="n">
         <v>0</v>
@@ -12266,13 +12266,13 @@
         <v>0</v>
       </c>
       <c r="M223" t="n">
-        <v>282.6336826383926</v>
+        <v>282.6336826383925</v>
       </c>
       <c r="N223" t="n">
-        <v>186.888852216397</v>
+        <v>186.8888522163969</v>
       </c>
       <c r="O223" t="n">
-        <v>56.05284723581521</v>
+        <v>56.05284723581519</v>
       </c>
       <c r="P223" t="n">
         <v>0</v>
@@ -12319,13 +12319,13 @@
         <v>0</v>
       </c>
       <c r="M224" t="n">
-        <v>262.5895840225115</v>
+        <v>262.589584022512</v>
       </c>
       <c r="N224" t="n">
-        <v>173.2931095327798</v>
+        <v>173.2931095327804</v>
       </c>
       <c r="O224" t="n">
-        <v>52.9919646597233</v>
+        <v>52.99196465972343</v>
       </c>
       <c r="P224" t="n">
         <v>0</v>
@@ -12372,13 +12372,13 @@
         <v>0</v>
       </c>
       <c r="M225" t="n">
-        <v>335.9094316799116</v>
+        <v>335.9094316799131</v>
       </c>
       <c r="N225" t="n">
-        <v>222.9906603580082</v>
+        <v>222.9906603580103</v>
       </c>
       <c r="O225" t="n">
-        <v>63.92914355954875</v>
+        <v>63.92914355954911</v>
       </c>
       <c r="P225" t="n">
         <v>0</v>
@@ -12425,13 +12425,13 @@
         <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>339.9792494610078</v>
+        <v>339.979249461006</v>
       </c>
       <c r="N226" t="n">
-        <v>225.7473291540097</v>
+        <v>225.7473291540072</v>
       </c>
       <c r="O226" t="n">
-        <v>64.51703689343913</v>
+        <v>64.51703689343869</v>
       </c>
       <c r="P226" t="n">
         <v>0</v>
@@ -12478,13 +12478,13 @@
         <v>0</v>
       </c>
       <c r="M227" t="n">
-        <v>336.9270620926255</v>
+        <v>336.9270620926245</v>
       </c>
       <c r="N227" t="n">
-        <v>223.6800586995365</v>
+        <v>223.6800586995351</v>
       </c>
       <c r="O227" t="n">
-        <v>64.07632681333446</v>
+        <v>64.07632681333422</v>
       </c>
       <c r="P227" t="n">
         <v>0</v>
@@ -12531,13 +12531,13 @@
         <v>0</v>
       </c>
       <c r="M228" t="n">
-        <v>262.5951061568649</v>
+        <v>262.5951061568653</v>
       </c>
       <c r="N228" t="n">
-        <v>173.3003981531491</v>
+        <v>173.3003981531496</v>
       </c>
       <c r="O228" t="n">
-        <v>52.99335765822521</v>
+        <v>52.99335765822531</v>
       </c>
       <c r="P228" t="n">
         <v>0</v>
@@ -12584,13 +12584,13 @@
         <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>285.0247406165881</v>
+        <v>285.0247406165892</v>
       </c>
       <c r="N229" t="n">
-        <v>188.5191182125816</v>
+        <v>188.519118212583</v>
       </c>
       <c r="O229" t="n">
-        <v>56.41548675872217</v>
+        <v>56.41548675872242</v>
       </c>
       <c r="P229" t="n">
         <v>0</v>
@@ -12637,13 +12637,13 @@
         <v>0</v>
       </c>
       <c r="M230" t="n">
-        <v>269.0524319079295</v>
+        <v>269.0524319079293</v>
       </c>
       <c r="N230" t="n">
-        <v>177.6817699907819</v>
+        <v>177.6817699907816</v>
       </c>
       <c r="O230" t="n">
-        <v>53.98593983838025</v>
+        <v>53.9859398383802</v>
       </c>
       <c r="P230" t="n">
         <v>0</v>
@@ -12743,13 +12743,13 @@
         <v>0</v>
       </c>
       <c r="M232" t="n">
-        <v>286.3713477069653</v>
+        <v>286.3713477069642</v>
       </c>
       <c r="N232" t="n">
-        <v>189.424631996176</v>
+        <v>189.4246319961747</v>
       </c>
       <c r="O232" t="n">
-        <v>56.61749063699755</v>
+        <v>56.6174906369973</v>
       </c>
       <c r="P232" t="n">
         <v>0</v>
@@ -12796,13 +12796,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M233" t="n">
-        <v>6447.518456562162</v>
+        <v>6447.518456562152</v>
       </c>
       <c r="N233" t="n">
-        <v>167.8261764248068</v>
+        <v>167.8261764248062</v>
       </c>
       <c r="O233" t="n">
-        <v>116.0855059588184</v>
+        <v>116.0855059588182</v>
       </c>
       <c r="P233" t="n">
         <v>0</v>
@@ -12849,13 +12849,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M234" t="n">
-        <v>4627.179410467784</v>
+        <v>4627.179410467786</v>
       </c>
       <c r="N234" t="n">
-        <v>119.3829760968357</v>
+        <v>119.3829760968358</v>
       </c>
       <c r="O234" t="n">
-        <v>90.11566363500215</v>
+        <v>90.11566363500218</v>
       </c>
       <c r="P234" t="n">
         <v>1</v>
@@ -12902,13 +12902,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M235" t="n">
-        <v>5763.322542711449</v>
+        <v>5763.322542711444</v>
       </c>
       <c r="N235" t="n">
-        <v>149.6330763053202</v>
+        <v>149.6330763053199</v>
       </c>
       <c r="O235" t="n">
-        <v>106.5815504583352</v>
+        <v>106.5815504583351</v>
       </c>
       <c r="P235" t="n">
         <v>0</v>
@@ -12955,13 +12955,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M236" t="n">
-        <v>5745.307971781628</v>
+        <v>5745.307971781638</v>
       </c>
       <c r="N236" t="n">
-        <v>149.1538514052736</v>
+        <v>149.1538514052741</v>
       </c>
       <c r="O236" t="n">
-        <v>106.3274906176104</v>
+        <v>106.3274906176106</v>
       </c>
       <c r="P236" t="n">
         <v>0</v>
@@ -13061,13 +13061,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M238" t="n">
-        <v>4627.179410467784</v>
+        <v>4627.179410467786</v>
       </c>
       <c r="N238" t="n">
-        <v>119.3829760968357</v>
+        <v>119.3829760968358</v>
       </c>
       <c r="O238" t="n">
-        <v>90.11566363500215</v>
+        <v>90.11566363500218</v>
       </c>
       <c r="P238" t="n">
         <v>1</v>
@@ -13167,13 +13167,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M240" t="n">
-        <v>545.4471693505831</v>
+        <v>545.4471693505828</v>
       </c>
       <c r="N240" t="n">
-        <v>653.9355298820844</v>
+        <v>653.935529882084</v>
       </c>
       <c r="O240" t="n">
-        <v>123.582119748969</v>
+        <v>123.5821197489689</v>
       </c>
       <c r="P240" t="n">
         <v>1</v>
@@ -13220,13 +13220,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M241" t="n">
-        <v>526.1576122187457</v>
+        <v>526.1576122187458</v>
       </c>
       <c r="N241" t="n">
-        <v>629.2689077973988</v>
+        <v>629.268907797399</v>
       </c>
       <c r="O241" t="n">
-        <v>120.1426207803227</v>
+        <v>120.1426207803228</v>
       </c>
       <c r="P241" t="n">
         <v>1</v>
@@ -13273,10 +13273,10 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M242" t="n">
-        <v>531.973351692763</v>
+        <v>531.9733516927629</v>
       </c>
       <c r="N242" t="n">
-        <v>636.7371985269026</v>
+        <v>636.7371985269023</v>
       </c>
       <c r="O242" t="n">
         <v>121.1860361789312</v>
@@ -13326,13 +13326,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M243" t="n">
-        <v>514.5612686246806</v>
+        <v>514.5612686246808</v>
       </c>
       <c r="N243" t="n">
-        <v>614.4187612557156</v>
+        <v>614.4187612557159</v>
       </c>
       <c r="O243" t="n">
-        <v>118.0569360074207</v>
+        <v>118.0569360074208</v>
       </c>
       <c r="P243" t="n">
         <v>1</v>
@@ -13379,13 +13379,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M244" t="n">
-        <v>601.9872375746028</v>
+        <v>601.987237574602</v>
       </c>
       <c r="N244" t="n">
-        <v>726.2277550440568</v>
+        <v>726.227755044055</v>
       </c>
       <c r="O244" t="n">
-        <v>133.4852386965152</v>
+        <v>133.485238696515</v>
       </c>
       <c r="P244" t="n">
         <v>1</v>
@@ -13435,10 +13435,10 @@
         <v>531.9659308861384</v>
       </c>
       <c r="N245" t="n">
-        <v>636.7194342135234</v>
+        <v>636.7194342135236</v>
       </c>
       <c r="O245" t="n">
-        <v>121.1839230642208</v>
+        <v>121.1839230642209</v>
       </c>
       <c r="P245" t="n">
         <v>1</v>
@@ -13594,10 +13594,10 @@
         <v>11594.08491255935</v>
       </c>
       <c r="N248" t="n">
-        <v>580.7676870400032</v>
+        <v>580.7676870400037</v>
       </c>
       <c r="O248" t="n">
-        <v>250.0692788262545</v>
+        <v>250.0692788262546</v>
       </c>
       <c r="P248" t="n">
         <v>1</v>
@@ -13644,13 +13644,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M249" t="n">
-        <v>11521.49728999641</v>
+        <v>11521.49728999642</v>
       </c>
       <c r="N249" t="n">
-        <v>576.8920107174204</v>
+        <v>576.892010717421</v>
       </c>
       <c r="O249" t="n">
-        <v>248.8424638612204</v>
+        <v>248.8424638612206</v>
       </c>
       <c r="P249" t="n">
         <v>1</v>
@@ -13700,10 +13700,10 @@
         <v>11339.9912616474</v>
       </c>
       <c r="N250" t="n">
-        <v>567.2000106120272</v>
+        <v>567.2000106120267</v>
       </c>
       <c r="O250" t="n">
-        <v>245.7657136620889</v>
+        <v>245.7657136620887</v>
       </c>
       <c r="P250" t="n">
         <v>1</v>
@@ -13750,13 +13750,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M251" t="n">
-        <v>586.4054284699171</v>
+        <v>586.405428469918</v>
       </c>
       <c r="N251" t="n">
-        <v>706.8432775606276</v>
+        <v>706.8432775606298</v>
       </c>
       <c r="O251" t="n">
-        <v>130.8311206755606</v>
+        <v>130.8311206755609</v>
       </c>
       <c r="P251" t="n">
         <v>0</v>
@@ -13803,13 +13803,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M252" t="n">
-        <v>597.9629392709616</v>
+        <v>597.9629392709608</v>
       </c>
       <c r="N252" t="n">
-        <v>721.6170306421643</v>
+        <v>721.6170306421624</v>
       </c>
       <c r="O252" t="n">
-        <v>132.8378855665989</v>
+        <v>132.8378855665986</v>
       </c>
       <c r="P252" t="n">
         <v>0</v>
@@ -13856,13 +13856,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M253" t="n">
-        <v>599.8890470185326</v>
+        <v>599.889047018533</v>
       </c>
       <c r="N253" t="n">
-        <v>724.0791623005698</v>
+        <v>724.0791623005708</v>
       </c>
       <c r="O253" t="n">
-        <v>133.1713363553162</v>
+        <v>133.1713363553163</v>
       </c>
       <c r="P253" t="n">
         <v>1</v>
@@ -13909,13 +13909,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M254" t="n">
-        <v>542.0633060869264</v>
+        <v>542.0633060869267</v>
       </c>
       <c r="N254" t="n">
-        <v>650.1382257650952</v>
+        <v>650.1382257650957</v>
       </c>
       <c r="O254" t="n">
-        <v>123.0312264257187</v>
+        <v>123.0312264257188</v>
       </c>
       <c r="P254" t="n">
         <v>0</v>
@@ -13962,13 +13962,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M255" t="n">
-        <v>563.2782201163982</v>
+        <v>563.2782201163983</v>
       </c>
       <c r="N255" t="n">
-        <v>677.272594076618</v>
+        <v>677.2725940766185</v>
       </c>
       <c r="O255" t="n">
-        <v>126.783428201181</v>
+        <v>126.7834282011811</v>
       </c>
       <c r="P255" t="n">
         <v>0</v>
@@ -14015,10 +14015,10 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M256" t="n">
-        <v>443.4778117667661</v>
+        <v>443.4778117667663</v>
       </c>
       <c r="N256" t="n">
-        <v>523.9332509253592</v>
+        <v>523.9332509253594</v>
       </c>
       <c r="O256" t="n">
         <v>105.0403003002145</v>
@@ -14068,13 +14068,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M257" t="n">
-        <v>607.5912103791836</v>
+        <v>607.5912103791838</v>
       </c>
       <c r="N257" t="n">
-        <v>733.9227267516268</v>
+        <v>733.9227267516272</v>
       </c>
       <c r="O257" t="n">
-        <v>134.5017821587901</v>
+        <v>134.5017821587902</v>
       </c>
       <c r="P257" t="n">
         <v>0</v>
@@ -14174,13 +14174,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M259" t="n">
-        <v>591.9705926859946</v>
+        <v>591.970592685994</v>
       </c>
       <c r="N259" t="n">
-        <v>713.9573762727355</v>
+        <v>713.957376272734</v>
       </c>
       <c r="O259" t="n">
-        <v>131.7987148831467</v>
+        <v>131.7987148831466</v>
       </c>
       <c r="P259" t="n">
         <v>1</v>
@@ -14227,13 +14227,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M260" t="n">
-        <v>630.6976637291586</v>
+        <v>630.6976637291594</v>
       </c>
       <c r="N260" t="n">
-        <v>763.4579958576956</v>
+        <v>763.4579958576971</v>
       </c>
       <c r="O260" t="n">
-        <v>138.4675090350015</v>
+        <v>138.4675090350017</v>
       </c>
       <c r="P260" t="n">
         <v>1</v>
@@ -14280,13 +14280,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M261" t="n">
-        <v>626.852216173456</v>
+        <v>626.8522161734554</v>
       </c>
       <c r="N261" t="n">
-        <v>758.5486055821418</v>
+        <v>758.5486055821405</v>
       </c>
       <c r="O261" t="n">
-        <v>137.8107190003997</v>
+        <v>137.8107190003995</v>
       </c>
       <c r="P261" t="n">
         <v>1</v>
@@ -14333,13 +14333,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M262" t="n">
-        <v>646.0855039104105</v>
+        <v>646.0855039104098</v>
       </c>
       <c r="N262" t="n">
-        <v>783.1118921087967</v>
+        <v>783.111892108795</v>
       </c>
       <c r="O262" t="n">
-        <v>141.0861585482781</v>
+        <v>141.0861585482779</v>
       </c>
       <c r="P262" t="n">
         <v>1</v>
@@ -14386,13 +14386,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M263" t="n">
-        <v>592.211711912144</v>
+        <v>592.2117119121434</v>
       </c>
       <c r="N263" t="n">
-        <v>714.2963148021286</v>
+        <v>714.2963148021271</v>
       </c>
       <c r="O263" t="n">
-        <v>131.8434177896022</v>
+        <v>131.843417789602</v>
       </c>
       <c r="P263" t="n">
         <v>1</v>
@@ -14439,13 +14439,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M264" t="n">
-        <v>558.4672602310224</v>
+        <v>558.4672602310231</v>
       </c>
       <c r="N264" t="n">
-        <v>671.1304763667468</v>
+        <v>671.1304763667488</v>
       </c>
       <c r="O264" t="n">
-        <v>125.9368742405635</v>
+        <v>125.9368742405638</v>
       </c>
       <c r="P264" t="n">
         <v>1</v>
@@ -14492,13 +14492,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M265" t="n">
-        <v>623.4815018551174</v>
+        <v>623.4815018551166</v>
       </c>
       <c r="N265" t="n">
-        <v>754.2386404928153</v>
+        <v>754.2386404928137</v>
       </c>
       <c r="O265" t="n">
-        <v>137.2335450342102</v>
+        <v>137.23354503421</v>
       </c>
       <c r="P265" t="n">
         <v>1</v>
@@ -14545,10 +14545,10 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M266" t="n">
-        <v>9106.579941017304</v>
+        <v>9106.579941017306</v>
       </c>
       <c r="N266" t="n">
-        <v>344.2042340404358</v>
+        <v>344.2042340404359</v>
       </c>
       <c r="O266" t="n">
         <v>181.2370273293099</v>
@@ -14601,10 +14601,10 @@
         <v>8505.878581788322</v>
       </c>
       <c r="N267" t="n">
-        <v>320.0718564375033</v>
+        <v>320.0718564375035</v>
       </c>
       <c r="O267" t="n">
-        <v>171.812018130896</v>
+        <v>171.8120181308961</v>
       </c>
       <c r="P267" t="n">
         <v>1</v>
@@ -14651,13 +14651,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M268" t="n">
-        <v>8615.153023940449</v>
+        <v>8615.153023940446</v>
       </c>
       <c r="N268" t="n">
-        <v>324.4627830640886</v>
+        <v>324.4627830640883</v>
       </c>
       <c r="O268" t="n">
-        <v>173.5394407155903</v>
+        <v>173.5394407155902</v>
       </c>
       <c r="P268" t="n">
         <v>1</v>
@@ -14707,7 +14707,7 @@
         <v>8888.228496168964</v>
       </c>
       <c r="N269" t="n">
-        <v>335.4337637138017</v>
+        <v>335.4337637138016</v>
       </c>
       <c r="O269" t="n">
         <v>177.8308851960889</v>
@@ -14757,13 +14757,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M270" t="n">
-        <v>7835.97549880135</v>
+        <v>7835.975498801353</v>
       </c>
       <c r="N270" t="n">
-        <v>293.1440495355137</v>
+        <v>293.1440495355139</v>
       </c>
       <c r="O270" t="n">
-        <v>161.088229709504</v>
+        <v>161.0882297095041</v>
       </c>
       <c r="P270" t="n">
         <v>1</v>
@@ -14810,13 +14810,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M271" t="n">
-        <v>8758.536990435476</v>
+        <v>8758.536990435474</v>
       </c>
       <c r="N271" t="n">
-        <v>330.2236615691105</v>
+        <v>330.2236615691104</v>
       </c>
       <c r="O271" t="n">
-        <v>175.797213292441</v>
+        <v>175.7972132924409</v>
       </c>
       <c r="P271" t="n">
         <v>1</v>
@@ -14863,10 +14863,10 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M272" t="n">
-        <v>9106.579941017304</v>
+        <v>9106.579941017306</v>
       </c>
       <c r="N272" t="n">
-        <v>344.2042340404358</v>
+        <v>344.2042340404359</v>
       </c>
       <c r="O272" t="n">
         <v>181.2370273293099</v>
@@ -14919,10 +14919,10 @@
         <v>8505.878581788322</v>
       </c>
       <c r="N273" t="n">
-        <v>320.0718564375033</v>
+        <v>320.0718564375035</v>
       </c>
       <c r="O273" t="n">
-        <v>171.812018130896</v>
+        <v>171.8120181308961</v>
       </c>
       <c r="P273" t="n">
         <v>1</v>
@@ -14969,10 +14969,10 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M274" t="n">
-        <v>8697.092028240211</v>
+        <v>8697.092028240215</v>
       </c>
       <c r="N274" t="n">
-        <v>327.7550181204832</v>
+        <v>327.7550181204835</v>
       </c>
       <c r="O274" t="n">
         <v>174.8308991963391</v>
@@ -15022,13 +15022,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M275" t="n">
-        <v>400.2818659724841</v>
+        <v>400.2818659724842</v>
       </c>
       <c r="N275" t="n">
-        <v>360.5058350025358</v>
+        <v>360.5058350025361</v>
       </c>
       <c r="O275" t="n">
-        <v>84.92736079072056</v>
+        <v>84.9273607907206</v>
       </c>
       <c r="P275" t="n">
         <v>1</v>
@@ -15075,13 +15075,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M276" t="n">
-        <v>401.730918678782</v>
+        <v>401.7309186787822</v>
       </c>
       <c r="N276" t="n">
-        <v>361.8980513929861</v>
+        <v>361.8980513929864</v>
       </c>
       <c r="O276" t="n">
-        <v>85.16809569926602</v>
+        <v>85.16809569926609</v>
       </c>
       <c r="P276" t="n">
         <v>1</v>
@@ -15128,13 +15128,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M277" t="n">
-        <v>394.5155919261083</v>
+        <v>394.5155919261081</v>
       </c>
       <c r="N277" t="n">
-        <v>354.9912681033549</v>
+        <v>354.9912681033547</v>
       </c>
       <c r="O277" t="n">
-        <v>83.97014019947324</v>
+        <v>83.97014019947322</v>
       </c>
       <c r="P277" t="n">
         <v>1</v>
@@ -15234,13 +15234,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M279" t="n">
-        <v>455.4023128233292</v>
+        <v>455.4023128233296</v>
       </c>
       <c r="N279" t="n">
-        <v>413.538716220931</v>
+        <v>413.5387162209317</v>
       </c>
       <c r="O279" t="n">
-        <v>93.9413713247708</v>
+        <v>93.94137132477091</v>
       </c>
       <c r="P279" t="n">
         <v>1</v>
@@ -15287,13 +15287,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M280" t="n">
-        <v>465.5596502149865</v>
+        <v>465.5596502149871</v>
       </c>
       <c r="N280" t="n">
-        <v>423.3196863264031</v>
+        <v>423.3196863264043</v>
       </c>
       <c r="O280" t="n">
-        <v>95.57142601351023</v>
+        <v>95.5714260135104</v>
       </c>
       <c r="P280" t="n">
         <v>1</v>
@@ -15340,13 +15340,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M281" t="n">
-        <v>445.2612061093454</v>
+        <v>445.2612061093457</v>
       </c>
       <c r="N281" t="n">
-        <v>403.7886825357652</v>
+        <v>403.7886825357658</v>
       </c>
       <c r="O281" t="n">
-        <v>92.30618154070912</v>
+        <v>92.30618154070922</v>
       </c>
       <c r="P281" t="n">
         <v>0</v>
@@ -15393,13 +15393,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M282" t="n">
-        <v>279.4093459994895</v>
+        <v>279.4093459994898</v>
       </c>
       <c r="N282" t="n">
-        <v>244.103739380708</v>
+        <v>244.1037393807085</v>
       </c>
       <c r="O282" t="n">
-        <v>63.87743200843215</v>
+        <v>63.87743200843223</v>
       </c>
       <c r="P282" t="n">
         <v>0</v>
@@ -15446,13 +15446,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M283" t="n">
-        <v>465.8964178640913</v>
+        <v>465.896417864092</v>
       </c>
       <c r="N283" t="n">
-        <v>423.9323336501953</v>
+        <v>423.9323336501968</v>
       </c>
       <c r="O283" t="n">
-        <v>95.65784961713297</v>
+        <v>95.65784961713317</v>
       </c>
       <c r="P283" t="n">
         <v>0</v>
@@ -15499,13 +15499,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M284" t="n">
-        <v>447.0608476141877</v>
+        <v>447.0608476141883</v>
       </c>
       <c r="N284" t="n">
-        <v>405.818282828094</v>
+        <v>405.8182828280953</v>
       </c>
       <c r="O284" t="n">
-        <v>92.63123701328152</v>
+        <v>92.63123701328171</v>
       </c>
       <c r="P284" t="n">
         <v>0</v>
@@ -15552,13 +15552,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M285" t="n">
-        <v>451.4086651328163</v>
+        <v>451.408665132817</v>
       </c>
       <c r="N285" t="n">
-        <v>410.0001043864301</v>
+        <v>410.0001043864312</v>
       </c>
       <c r="O285" t="n">
-        <v>93.33283472286348</v>
+        <v>93.33283472286365</v>
       </c>
       <c r="P285" t="n">
         <v>1</v>
@@ -15608,10 +15608,10 @@
         <v>308.9082584939189</v>
       </c>
       <c r="N286" t="n">
-        <v>272.7566170536477</v>
+        <v>272.7566170536479</v>
       </c>
       <c r="O286" t="n">
-        <v>69.2380817905205</v>
+        <v>69.23808179052051</v>
       </c>
       <c r="P286" t="n">
         <v>0</v>
@@ -15658,13 +15658,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M287" t="n">
-        <v>333.7113477973834</v>
+        <v>333.7113477973833</v>
       </c>
       <c r="N287" t="n">
-        <v>296.6703333197248</v>
+        <v>296.6703333197245</v>
       </c>
       <c r="O287" t="n">
-        <v>73.61728616529781</v>
+        <v>73.61728616529777</v>
       </c>
       <c r="P287" t="n">
         <v>1</v>
@@ -15711,13 +15711,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M288" t="n">
-        <v>452.857777359607</v>
+        <v>452.8577773596068</v>
       </c>
       <c r="N288" t="n">
-        <v>411.3938128920927</v>
+        <v>411.3938128920924</v>
       </c>
       <c r="O288" t="n">
-        <v>93.56627406244556</v>
+        <v>93.56627406244552</v>
       </c>
       <c r="P288" t="n">
         <v>1</v>
@@ -15764,13 +15764,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M289" t="n">
-        <v>452.8577901267775</v>
+        <v>452.8577901267766</v>
       </c>
       <c r="N289" t="n">
-        <v>411.3938360884924</v>
+        <v>411.3938360884908</v>
       </c>
       <c r="O289" t="n">
-        <v>93.56627735977376</v>
+        <v>93.56627735977351</v>
       </c>
       <c r="P289" t="n">
         <v>1</v>
@@ -15817,13 +15817,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M290" t="n">
-        <v>457.2046581001742</v>
+        <v>457.2046581001745</v>
       </c>
       <c r="N290" t="n">
-        <v>415.5742827810571</v>
+        <v>415.5742827810578</v>
       </c>
       <c r="O290" t="n">
-        <v>94.2653303028024</v>
+        <v>94.26533030280248</v>
       </c>
       <c r="P290" t="n">
         <v>0</v>
@@ -15870,13 +15870,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M291" t="n">
-        <v>451.4087038090905</v>
+        <v>451.4087038090911</v>
       </c>
       <c r="N291" t="n">
-        <v>410.0001746432877</v>
+        <v>410.0001746432886</v>
       </c>
       <c r="O291" t="n">
-        <v>93.33284471870158</v>
+        <v>93.33284471870171</v>
       </c>
       <c r="P291" t="n">
         <v>0</v>
@@ -15923,13 +15923,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M292" t="n">
-        <v>494.8528974843455</v>
+        <v>494.8528974843447</v>
       </c>
       <c r="N292" t="n">
-        <v>451.7698161869017</v>
+        <v>451.7698161869002</v>
       </c>
       <c r="O292" t="n">
-        <v>100.2484427447364</v>
+        <v>100.2484427447362</v>
       </c>
       <c r="P292" t="n">
         <v>1</v>
@@ -15976,13 +15976,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M293" t="n">
-        <v>477.4841481223018</v>
+        <v>477.4841481223019</v>
       </c>
       <c r="N293" t="n">
-        <v>435.0755395963444</v>
+        <v>435.0755395963446</v>
       </c>
       <c r="O293" t="n">
-        <v>97.50391934035903</v>
+        <v>97.50391934035906</v>
       </c>
       <c r="P293" t="n">
         <v>1</v>
@@ -16029,13 +16029,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M294" t="n">
-        <v>489.064243671167</v>
+        <v>489.0642436711677</v>
       </c>
       <c r="N294" t="n">
-        <v>446.2063906264052</v>
+        <v>446.2063906264064</v>
       </c>
       <c r="O294" t="n">
-        <v>99.3366182319908</v>
+        <v>99.33661823199097</v>
       </c>
       <c r="P294" t="n">
         <v>1</v>
@@ -16082,13 +16082,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M295" t="n">
-        <v>481.8323214692657</v>
+        <v>481.8323214692655</v>
       </c>
       <c r="N295" t="n">
-        <v>439.2597127452713</v>
+        <v>439.2597127452709</v>
       </c>
       <c r="O295" t="n">
-        <v>98.19393607172631</v>
+        <v>98.19393607172627</v>
       </c>
       <c r="P295" t="n">
         <v>1</v>
@@ -16135,13 +16135,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M296" t="n">
-        <v>453.344875788954</v>
+        <v>453.3448757889539</v>
       </c>
       <c r="N296" t="n">
-        <v>411.865767737023</v>
+        <v>411.8657677370227</v>
       </c>
       <c r="O296" t="n">
-        <v>93.64509322150916</v>
+        <v>93.64509322150913</v>
       </c>
       <c r="P296" t="n">
         <v>1</v>
@@ -16188,13 +16188,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M297" t="n">
-        <v>445.4584182780342</v>
+        <v>445.4584182780335</v>
       </c>
       <c r="N297" t="n">
-        <v>404.2838199384023</v>
+        <v>404.2838199384011</v>
       </c>
       <c r="O297" t="n">
-        <v>92.37298393982299</v>
+        <v>92.3729839398228</v>
       </c>
       <c r="P297" t="n">
         <v>1</v>
@@ -16241,13 +16241,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M298" t="n">
-        <v>254.7826484298542</v>
+        <v>254.7826484298531</v>
       </c>
       <c r="N298" t="n">
-        <v>119.758037840147</v>
+        <v>119.758037840146</v>
       </c>
       <c r="O298" t="n">
-        <v>43.72147427544969</v>
+        <v>43.72147427544946</v>
       </c>
       <c r="P298" t="n">
         <v>1</v>
@@ -16294,13 +16294,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M299" t="n">
-        <v>252.6261563012322</v>
+        <v>252.6261563012324</v>
       </c>
       <c r="N299" t="n">
-        <v>118.7259846973342</v>
+        <v>118.7259846973344</v>
       </c>
       <c r="O299" t="n">
-        <v>43.44026527830602</v>
+        <v>43.44026527830608</v>
       </c>
       <c r="P299" t="n">
         <v>0</v>
@@ -16347,13 +16347,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M300" t="n">
-        <v>254.7822956136416</v>
+        <v>254.7822956136422</v>
       </c>
       <c r="N300" t="n">
-        <v>119.7577061649066</v>
+        <v>119.7577061649072</v>
       </c>
       <c r="O300" t="n">
-        <v>43.72139859504922</v>
+        <v>43.72139859504936</v>
       </c>
       <c r="P300" t="n">
         <v>1</v>
@@ -16400,13 +16400,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M301" t="n">
-        <v>249.0313897837816</v>
+        <v>249.0313897837825</v>
       </c>
       <c r="N301" t="n">
-        <v>117.0053331107477</v>
+        <v>117.0053331107485</v>
       </c>
       <c r="O301" t="n">
-        <v>42.97009875123848</v>
+        <v>42.97009875123867</v>
       </c>
       <c r="P301" t="n">
         <v>1</v>
@@ -16453,13 +16453,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M302" t="n">
-        <v>199.8532870958966</v>
+        <v>199.8532870958972</v>
       </c>
       <c r="N302" t="n">
-        <v>93.44544869138547</v>
+        <v>93.44544869138598</v>
       </c>
       <c r="O302" t="n">
-        <v>36.34602331004499</v>
+        <v>36.34602331004511</v>
       </c>
       <c r="P302" t="n">
         <v>0</v>
@@ -16506,13 +16506,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M303" t="n">
-        <v>185.6842788735838</v>
+        <v>185.6842788735843</v>
       </c>
       <c r="N303" t="n">
-        <v>86.65159775048051</v>
+        <v>86.65159775048097</v>
       </c>
       <c r="O303" t="n">
-        <v>34.36228783213244</v>
+        <v>34.36228783213256</v>
       </c>
       <c r="P303" t="n">
         <v>1</v>
@@ -16559,13 +16559,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M304" t="n">
-        <v>240.4000650196608</v>
+        <v>240.4000650196602</v>
       </c>
       <c r="N304" t="n">
-        <v>112.8721924103358</v>
+        <v>112.8721924103352</v>
       </c>
       <c r="O304" t="n">
-        <v>41.83378167908916</v>
+        <v>41.83378167908901</v>
       </c>
       <c r="P304" t="n">
         <v>0</v>
@@ -16612,13 +16612,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M305" t="n">
-        <v>237.5229370182673</v>
+        <v>237.5229370182675</v>
       </c>
       <c r="N305" t="n">
-        <v>111.4944852602626</v>
+        <v>111.4944852602628</v>
       </c>
       <c r="O305" t="n">
-        <v>41.45272469815998</v>
+        <v>41.45272469816003</v>
       </c>
       <c r="P305" t="n">
         <v>0</v>
@@ -16668,10 +16668,10 @@
         <v>234.6455594036302</v>
       </c>
       <c r="N306" t="n">
-        <v>110.1165570647191</v>
+        <v>110.116557064719</v>
       </c>
       <c r="O306" t="n">
-        <v>41.07044391581825</v>
+        <v>41.07044391581824</v>
       </c>
       <c r="P306" t="n">
         <v>0</v>
@@ -16718,13 +16718,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M307" t="n">
-        <v>245.4344268201697</v>
+        <v>245.4344268201689</v>
       </c>
       <c r="N307" t="n">
-        <v>115.2826352859103</v>
+        <v>115.2826352859096</v>
       </c>
       <c r="O307" t="n">
-        <v>42.49773831545576</v>
+        <v>42.49773831545558</v>
       </c>
       <c r="P307" t="n">
         <v>0</v>
@@ -16771,13 +16771,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M308" t="n">
-        <v>241.838538358939</v>
+        <v>241.8385383589372</v>
       </c>
       <c r="N308" t="n">
-        <v>113.5609656597891</v>
+        <v>113.5609656597874</v>
       </c>
       <c r="O308" t="n">
-        <v>42.02385756188458</v>
+        <v>42.02385756188418</v>
       </c>
       <c r="P308" t="n">
         <v>0</v>
@@ -16824,13 +16824,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M309" t="n">
-        <v>190.244391593645</v>
+        <v>190.2443915936455</v>
       </c>
       <c r="N309" t="n">
-        <v>88.83676868086383</v>
+        <v>88.83676868086422</v>
       </c>
       <c r="O309" t="n">
-        <v>35.004537372515</v>
+        <v>35.0045373725151</v>
       </c>
       <c r="P309" t="n">
         <v>0</v>
@@ -16877,13 +16877,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M310" t="n">
-        <v>204.1741822418072</v>
+        <v>204.1741822418085</v>
       </c>
       <c r="N310" t="n">
-        <v>95.51654340781855</v>
+        <v>95.51654340781977</v>
       </c>
       <c r="O310" t="n">
-        <v>36.94362481134876</v>
+        <v>36.94362481134905</v>
       </c>
       <c r="P310" t="n">
         <v>0</v>
@@ -16930,13 +16930,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M311" t="n">
-        <v>185.6246629686898</v>
+        <v>185.6246629686904</v>
       </c>
       <c r="N311" t="n">
-        <v>86.5959658556085</v>
+        <v>86.59596585560902</v>
       </c>
       <c r="O311" t="n">
-        <v>34.34849791494056</v>
+        <v>34.34849791494069</v>
       </c>
       <c r="P311" t="n">
         <v>0</v>
@@ -16983,13 +16983,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M312" t="n">
-        <v>212.999584028189</v>
+        <v>212.9995840281887</v>
       </c>
       <c r="N312" t="n">
-        <v>99.72109996063934</v>
+        <v>99.72109996063902</v>
       </c>
       <c r="O312" t="n">
-        <v>38.14944454041512</v>
+        <v>38.14944454041505</v>
       </c>
       <c r="P312" t="n">
         <v>0</v>
@@ -17036,13 +17036,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M313" t="n">
-        <v>208.680037478775</v>
+        <v>208.6800374787751</v>
       </c>
       <c r="N313" t="n">
-        <v>97.65119020458407</v>
+        <v>97.65119020458415</v>
       </c>
       <c r="O313" t="n">
-        <v>37.55856553437054</v>
+        <v>37.55856553437056</v>
       </c>
       <c r="P313" t="n">
         <v>0</v>
@@ -17089,13 +17089,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M314" t="n">
-        <v>185.6204452938271</v>
+        <v>185.6204452938277</v>
       </c>
       <c r="N314" t="n">
-        <v>86.59203071602917</v>
+        <v>86.59203071602977</v>
       </c>
       <c r="O314" t="n">
-        <v>34.3475223550227</v>
+        <v>34.34752235502285</v>
       </c>
       <c r="P314" t="n">
         <v>0</v>
@@ -17142,13 +17142,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M315" t="n">
-        <v>177.688827638095</v>
+        <v>177.6888276380948</v>
       </c>
       <c r="N315" t="n">
-        <v>82.78634433374758</v>
+        <v>82.78634433374737</v>
       </c>
       <c r="O315" t="n">
-        <v>33.21959881253832</v>
+        <v>33.21959881253827</v>
       </c>
       <c r="P315" t="n">
         <v>0</v>
@@ -17195,13 +17195,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M316" t="n">
-        <v>191.3842643314833</v>
+        <v>191.3842643314831</v>
       </c>
       <c r="N316" t="n">
-        <v>89.35564320779997</v>
+        <v>89.35564320779977</v>
       </c>
       <c r="O316" t="n">
-        <v>35.15908380365378</v>
+        <v>35.15908380365373</v>
       </c>
       <c r="P316" t="n">
         <v>0</v>
@@ -17248,13 +17248,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M317" t="n">
-        <v>4485.914689656217</v>
+        <v>4485.914689656207</v>
       </c>
       <c r="N317" t="n">
-        <v>87.71177901924618</v>
+        <v>87.71177901924581</v>
       </c>
       <c r="O317" t="n">
-        <v>76.64639136584626</v>
+        <v>76.64639136584604</v>
       </c>
       <c r="P317" t="n">
         <v>0</v>
@@ -17301,13 +17301,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M318" t="n">
-        <v>4458.811258757667</v>
+        <v>4458.811258757669</v>
       </c>
       <c r="N318" t="n">
-        <v>87.16936349770563</v>
+        <v>87.1693634977057</v>
       </c>
       <c r="O318" t="n">
-        <v>76.29335434403927</v>
+        <v>76.2933543440393</v>
       </c>
       <c r="P318" t="n">
         <v>0</v>
@@ -17407,13 +17407,13 @@
         <v>0.7853981633974483</v>
       </c>
       <c r="M320" t="n">
-        <v>4384.269103609665</v>
+        <v>4384.269103609674</v>
       </c>
       <c r="N320" t="n">
-        <v>85.6774378904144</v>
+        <v>85.67743789041477</v>
       </c>
       <c r="O320" t="n">
-        <v>75.31951869950699</v>
+        <v>75.3195186995072</v>
       </c>
       <c r="P320" t="n">
         <v>0</v>
@@ -17460,10 +17460,10 @@
         <v>0</v>
       </c>
       <c r="M321" t="n">
-        <v>845.5248632614999</v>
+        <v>845.5248632615003</v>
       </c>
       <c r="N321" t="n">
-        <v>1540.871648936224</v>
+        <v>1540.871648936225</v>
       </c>
       <c r="O321" t="n">
         <v>211.6726895032407</v>
@@ -17513,13 +17513,13 @@
         <v>0</v>
       </c>
       <c r="M322" t="n">
-        <v>848.6095206340966</v>
+        <v>848.6095206340967</v>
       </c>
       <c r="N322" t="n">
-        <v>1547.128135313665</v>
+        <v>1547.128135313666</v>
       </c>
       <c r="O322" t="n">
-        <v>212.2951717103404</v>
+        <v>212.2951717103405</v>
       </c>
       <c r="P322" t="n">
         <v>1</v>
@@ -17566,13 +17566,13 @@
         <v>0</v>
       </c>
       <c r="M323" t="n">
-        <v>916.5695709010109</v>
+        <v>916.5695709010121</v>
       </c>
       <c r="N323" t="n">
-        <v>1685.25243995208</v>
+        <v>1685.252439952083</v>
       </c>
       <c r="O323" t="n">
-        <v>225.8779518215629</v>
+        <v>225.8779518215632</v>
       </c>
       <c r="P323" t="n">
         <v>1</v>
@@ -17619,13 +17619,13 @@
         <v>0</v>
       </c>
       <c r="M324" t="n">
-        <v>932.0020341578482</v>
+        <v>932.0020341578509</v>
       </c>
       <c r="N324" t="n">
-        <v>1716.627232177749</v>
+        <v>1716.627232177759</v>
       </c>
       <c r="O324" t="n">
-        <v>228.9244681871585</v>
+        <v>228.9244681871592</v>
       </c>
       <c r="P324" t="n">
         <v>1</v>
@@ -17672,13 +17672,13 @@
         <v>0</v>
       </c>
       <c r="M325" t="n">
-        <v>867.1517570161008</v>
+        <v>867.1517570160995</v>
       </c>
       <c r="N325" t="n">
-        <v>1584.803101186598</v>
+        <v>1584.803101186594</v>
       </c>
       <c r="O325" t="n">
-        <v>216.0286905977031</v>
+        <v>216.0286905977028</v>
       </c>
       <c r="P325" t="n">
         <v>1</v>
@@ -17725,13 +17725,13 @@
         <v>0</v>
       </c>
       <c r="M326" t="n">
-        <v>916.5825775355421</v>
+        <v>916.5825775355404</v>
       </c>
       <c r="N326" t="n">
-        <v>1685.300269639644</v>
+        <v>1685.300269639638</v>
       </c>
       <c r="O326" t="n">
-        <v>225.8819584966595</v>
+        <v>225.881958496659</v>
       </c>
       <c r="P326" t="n">
         <v>1</v>
@@ -17778,10 +17778,10 @@
         <v>0</v>
       </c>
       <c r="M327" t="n">
-        <v>860.9440282292734</v>
+        <v>860.9440282292737</v>
       </c>
       <c r="N327" t="n">
-        <v>1572.144157474374</v>
+        <v>1572.144157474375</v>
       </c>
       <c r="O327" t="n">
         <v>214.7780586529383</v>
@@ -17831,13 +17831,13 @@
         <v>0</v>
       </c>
       <c r="M328" t="n">
-        <v>842.3932814640372</v>
+        <v>842.393281464035</v>
       </c>
       <c r="N328" t="n">
-        <v>1534.444732328305</v>
+        <v>1534.444732328297</v>
       </c>
       <c r="O328" t="n">
-        <v>211.0349320832373</v>
+        <v>211.0349320832366</v>
       </c>
       <c r="P328" t="n">
         <v>1</v>
@@ -17884,13 +17884,13 @@
         <v>0</v>
       </c>
       <c r="M329" t="n">
-        <v>898.0199978608642</v>
+        <v>898.0199978608639</v>
       </c>
       <c r="N329" t="n">
-        <v>1647.504441748299</v>
+        <v>1647.504441748298</v>
       </c>
       <c r="O329" t="n">
-        <v>222.1952646028397</v>
+        <v>222.1952646028396</v>
       </c>
       <c r="P329" t="n">
         <v>0</v>
@@ -17937,13 +17937,13 @@
         <v>0</v>
       </c>
       <c r="M330" t="n">
-        <v>857.8532087723481</v>
+        <v>857.8532087723504</v>
       </c>
       <c r="N330" t="n">
-        <v>1565.863139048011</v>
+        <v>1565.86313904802</v>
       </c>
       <c r="O330" t="n">
-        <v>214.1559501458652</v>
+        <v>214.1559501458659</v>
       </c>
       <c r="P330" t="n">
         <v>0</v>
@@ -17990,13 +17990,13 @@
         <v>0</v>
       </c>
       <c r="M331" t="n">
-        <v>882.5755878379167</v>
+        <v>882.5755878379193</v>
       </c>
       <c r="N331" t="n">
-        <v>1616.110184202419</v>
+        <v>1616.110184202429</v>
       </c>
       <c r="O331" t="n">
-        <v>219.1156821384177</v>
+        <v>219.1156821384185</v>
       </c>
       <c r="P331" t="n">
         <v>0</v>
@@ -18043,13 +18043,13 @@
         <v>0</v>
       </c>
       <c r="M332" t="n">
-        <v>867.1254253088058</v>
+        <v>867.1254253088042</v>
       </c>
       <c r="N332" t="n">
-        <v>1584.706855200926</v>
+        <v>1584.70685520092</v>
       </c>
       <c r="O332" t="n">
-        <v>216.0204907892349</v>
+        <v>216.0204907892344</v>
       </c>
       <c r="P332" t="n">
         <v>1</v>
@@ -18096,13 +18096,13 @@
         <v>0</v>
       </c>
       <c r="M333" t="n">
-        <v>743.3078134672651</v>
+        <v>743.3078134672666</v>
       </c>
       <c r="N333" t="n">
-        <v>1333.215923762751</v>
+        <v>1333.215923762756</v>
       </c>
       <c r="O333" t="n">
-        <v>190.6524631701324</v>
+        <v>190.6524631701329</v>
       </c>
       <c r="P333" t="n">
         <v>1</v>
@@ -18149,10 +18149,10 @@
         <v>0</v>
       </c>
       <c r="M334" t="n">
-        <v>609.7317481741203</v>
+        <v>609.7317481741201</v>
       </c>
       <c r="N334" t="n">
-        <v>1062.658878326213</v>
+        <v>1062.658878326212</v>
       </c>
       <c r="O334" t="n">
         <v>161.9875510516702</v>
@@ -18202,13 +18202,13 @@
         <v>0</v>
       </c>
       <c r="M335" t="n">
-        <v>662.6017418320132</v>
+        <v>662.6017418320137</v>
       </c>
       <c r="N335" t="n">
-        <v>1169.599882400639</v>
+        <v>1169.59988240064</v>
       </c>
       <c r="O335" t="n">
-        <v>173.5129131310974</v>
+        <v>173.5129131310975</v>
       </c>
       <c r="P335" t="n">
         <v>1</v>
@@ -18255,13 +18255,13 @@
         <v>0</v>
       </c>
       <c r="M336" t="n">
-        <v>575.4752745000699</v>
+        <v>575.4752745000691</v>
       </c>
       <c r="N336" t="n">
-        <v>993.5106827787414</v>
+        <v>993.5106827787386</v>
       </c>
       <c r="O336" t="n">
-        <v>154.3806758328357</v>
+        <v>154.3806758328355</v>
       </c>
       <c r="P336" t="n">
         <v>0</v>
@@ -18308,13 +18308,13 @@
         <v>0</v>
       </c>
       <c r="M337" t="n">
-        <v>600.3915650842412</v>
+        <v>600.3915650842415</v>
       </c>
       <c r="N337" t="n">
-        <v>1043.790900769387</v>
+        <v>1043.790900769388</v>
       </c>
       <c r="O337" t="n">
-        <v>159.9246462868773</v>
+        <v>159.9246462868774</v>
       </c>
       <c r="P337" t="n">
         <v>1</v>
@@ -18361,13 +18361,13 @@
         <v>0</v>
       </c>
       <c r="M338" t="n">
-        <v>990.5759456763218</v>
+        <v>990.5759456763228</v>
       </c>
       <c r="N338" t="n">
-        <v>1835.68321001076</v>
+        <v>1835.683210010764</v>
       </c>
       <c r="O338" t="n">
-        <v>240.3647690822535</v>
+        <v>240.3647690822538</v>
       </c>
       <c r="P338" t="n">
         <v>1</v>
@@ -18467,13 +18467,13 @@
         <v>0</v>
       </c>
       <c r="M340" t="n">
-        <v>16032.90589079017</v>
+        <v>16032.90589079014</v>
       </c>
       <c r="N340" t="n">
-        <v>1201.968265897374</v>
+        <v>1201.96826589737</v>
       </c>
       <c r="O340" t="n">
-        <v>390.1212092142057</v>
+        <v>390.121209214205</v>
       </c>
       <c r="P340" t="n">
         <v>1</v>
@@ -18520,13 +18520,13 @@
         <v>0</v>
       </c>
       <c r="M341" t="n">
-        <v>14516.80685964539</v>
+        <v>14516.8068596454</v>
       </c>
       <c r="N341" t="n">
-        <v>1073.741644066834</v>
+        <v>1073.741644066836</v>
       </c>
       <c r="O341" t="n">
-        <v>359.6811459784695</v>
+        <v>359.6811459784699</v>
       </c>
       <c r="P341" t="n">
         <v>1</v>
@@ -18573,13 +18573,13 @@
         <v>0</v>
       </c>
       <c r="M342" t="n">
-        <v>13932.89176382288</v>
+        <v>13932.89176382286</v>
       </c>
       <c r="N342" t="n">
-        <v>1024.42482187373</v>
+        <v>1024.424821873726</v>
       </c>
       <c r="O342" t="n">
-        <v>347.736567015335</v>
+        <v>347.7365670153343</v>
       </c>
       <c r="P342" t="n">
         <v>1</v>
@@ -18626,13 +18626,13 @@
         <v>0</v>
       </c>
       <c r="M343" t="n">
-        <v>14866.93991819769</v>
+        <v>14866.93991819765</v>
       </c>
       <c r="N343" t="n">
-        <v>1103.334146441875</v>
+        <v>1103.33414644187</v>
       </c>
       <c r="O343" t="n">
-        <v>366.7827700762867</v>
+        <v>366.7827700762855</v>
       </c>
       <c r="P343" t="n">
         <v>1</v>
@@ -18679,13 +18679,13 @@
         <v>0</v>
       </c>
       <c r="M344" t="n">
-        <v>16032.90589079017</v>
+        <v>16032.90589079014</v>
       </c>
       <c r="N344" t="n">
-        <v>1201.968265897374</v>
+        <v>1201.96826589737</v>
       </c>
       <c r="O344" t="n">
-        <v>390.1212092142057</v>
+        <v>390.121209214205</v>
       </c>
       <c r="P344" t="n">
         <v>1</v>
@@ -18732,13 +18732,13 @@
         <v>0</v>
       </c>
       <c r="M345" t="n">
-        <v>14983.61528314762</v>
+        <v>14983.61528314759</v>
       </c>
       <c r="N345" t="n">
-        <v>1113.198367407353</v>
+        <v>1113.198367407349</v>
       </c>
       <c r="O345" t="n">
-        <v>369.139427025914</v>
+        <v>369.1394270259131</v>
       </c>
       <c r="P345" t="n">
         <v>1</v>
@@ -18785,13 +18785,13 @@
         <v>0</v>
       </c>
       <c r="M346" t="n">
-        <v>15275.22635934235</v>
+        <v>15275.22635934233</v>
       </c>
       <c r="N346" t="n">
-        <v>1137.85855299467</v>
+        <v>1137.858552994667</v>
       </c>
       <c r="O346" t="n">
-        <v>375.0084492343581</v>
+        <v>375.0084492343576</v>
       </c>
       <c r="P346" t="n">
         <v>1</v>
@@ -18841,7 +18841,7 @@
         <v>11182.46369144625</v>
       </c>
       <c r="N347" t="n">
-        <v>793.0027072521144</v>
+        <v>793.0027072521142</v>
       </c>
       <c r="O347" t="n">
         <v>289.5820972988824</v>
@@ -18894,10 +18894,10 @@
         <v>12178.42259831476</v>
       </c>
       <c r="N348" t="n">
-        <v>876.5923360927212</v>
+        <v>876.5923360927214</v>
       </c>
       <c r="O348" t="n">
-        <v>311.0259281397563</v>
+        <v>311.0259281397564</v>
       </c>
       <c r="P348" t="n">
         <v>1</v>
@@ -18944,13 +18944,13 @@
         <v>0</v>
       </c>
       <c r="M349" t="n">
-        <v>17139.00306333657</v>
+        <v>17139.00306333658</v>
       </c>
       <c r="N349" t="n">
-        <v>1295.632708453932</v>
+        <v>1295.632708453933</v>
       </c>
       <c r="O349" t="n">
-        <v>411.8483598238574</v>
+        <v>411.8483598238577</v>
       </c>
       <c r="P349" t="n">
         <v>1</v>
@@ -18997,13 +18997,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M350" t="n">
-        <v>267.7452322760797</v>
+        <v>267.745232276078</v>
       </c>
       <c r="N350" t="n">
-        <v>166.354201369222</v>
+        <v>166.3542013692199</v>
       </c>
       <c r="O350" t="n">
-        <v>52.17318182927536</v>
+        <v>52.17318182927493</v>
       </c>
       <c r="P350" t="n">
         <v>0</v>
@@ -19050,13 +19050,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M351" t="n">
-        <v>278.2728733118739</v>
+        <v>278.2728733118735</v>
       </c>
       <c r="N351" t="n">
-        <v>173.0603823316137</v>
+        <v>173.0603823316133</v>
       </c>
       <c r="O351" t="n">
-        <v>53.7299637433889</v>
+        <v>53.72996374338882</v>
       </c>
       <c r="P351" t="n">
         <v>0</v>
@@ -19109,7 +19109,7 @@
         <v>146.2132932551649</v>
       </c>
       <c r="O352" t="n">
-        <v>47.40094273607685</v>
+        <v>47.40094273607684</v>
       </c>
       <c r="P352" t="n">
         <v>0</v>
@@ -19156,13 +19156,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M353" t="n">
-        <v>248.5937388992266</v>
+        <v>248.5937388992269</v>
       </c>
       <c r="N353" t="n">
-        <v>154.1492050385669</v>
+        <v>154.1492050385673</v>
       </c>
       <c r="O353" t="n">
-        <v>49.29957680609069</v>
+        <v>49.29957680609076</v>
       </c>
       <c r="P353" t="n">
         <v>0</v>
@@ -19209,13 +19209,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M354" t="n">
-        <v>260.0847860173456</v>
+        <v>260.084786017345</v>
       </c>
       <c r="N354" t="n">
-        <v>161.4722405975945</v>
+        <v>161.4722405975938</v>
       </c>
       <c r="O354" t="n">
-        <v>51.0302472882547</v>
+        <v>51.03024728825454</v>
       </c>
       <c r="P354" t="n">
         <v>0</v>
@@ -19315,13 +19315,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M356" t="n">
-        <v>313.6610678912168</v>
+        <v>313.6610678912151</v>
       </c>
       <c r="N356" t="n">
-        <v>195.5908817752274</v>
+        <v>195.5908817752253</v>
       </c>
       <c r="O356" t="n">
-        <v>58.85582564584291</v>
+        <v>58.85582564584254</v>
       </c>
       <c r="P356" t="n">
         <v>0</v>
@@ -19368,13 +19368,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M357" t="n">
-        <v>309.9145303387367</v>
+        <v>309.9145303387355</v>
       </c>
       <c r="N357" t="n">
-        <v>193.2538085958479</v>
+        <v>193.2538085958463</v>
       </c>
       <c r="O357" t="n">
-        <v>58.32765486939178</v>
+        <v>58.32765486939147</v>
       </c>
       <c r="P357" t="n">
         <v>0</v>
@@ -19421,13 +19421,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M358" t="n">
-        <v>312.7825768330984</v>
+        <v>312.7825768330975</v>
       </c>
       <c r="N358" t="n">
-        <v>195.0791334794682</v>
+        <v>195.0791334794671</v>
       </c>
       <c r="O358" t="n">
-        <v>58.73757968718133</v>
+        <v>58.73757968718113</v>
       </c>
       <c r="P358" t="n">
         <v>0</v>
@@ -19474,13 +19474,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M359" t="n">
-        <v>306.0901269109226</v>
+        <v>306.0901269109231</v>
       </c>
       <c r="N359" t="n">
-        <v>190.8196383483576</v>
+        <v>190.8196383483583</v>
       </c>
       <c r="O359" t="n">
-        <v>57.77951134166916</v>
+        <v>57.7795113416693</v>
       </c>
       <c r="P359" t="n">
         <v>0</v>
@@ -19527,13 +19527,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M360" t="n">
-        <v>316.6063215307883</v>
+        <v>316.6063215307887</v>
       </c>
       <c r="N360" t="n">
-        <v>197.5125253642566</v>
+        <v>197.5125253642572</v>
       </c>
       <c r="O360" t="n">
-        <v>59.28259643224797</v>
+        <v>59.28259643224807</v>
       </c>
       <c r="P360" t="n">
         <v>0</v>
@@ -19580,13 +19580,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M361" t="n">
-        <v>304.1777869046429</v>
+        <v>304.1777869046435</v>
       </c>
       <c r="N361" t="n">
-        <v>189.6023905832689</v>
+        <v>189.6023905832695</v>
       </c>
       <c r="O361" t="n">
-        <v>57.50475776406928</v>
+        <v>57.5047577640694</v>
       </c>
       <c r="P361" t="n">
         <v>0</v>
@@ -19636,10 +19636,10 @@
         <v>314.6945412348032</v>
       </c>
       <c r="N362" t="n">
-        <v>196.295941293481</v>
+        <v>196.2959412934809</v>
       </c>
       <c r="O362" t="n">
-        <v>59.01031900551489</v>
+        <v>59.01031900551487</v>
       </c>
       <c r="P362" t="n">
         <v>0</v>
@@ -19686,13 +19686,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M363" t="n">
-        <v>313.7385649909863</v>
+        <v>313.738564990986</v>
       </c>
       <c r="N363" t="n">
-        <v>195.6875440655864</v>
+        <v>195.6875440655861</v>
       </c>
       <c r="O363" t="n">
-        <v>58.87400329489423</v>
+        <v>58.87400329489418</v>
       </c>
       <c r="P363" t="n">
         <v>0</v>
@@ -19739,13 +19739,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M364" t="n">
-        <v>313.7385755734217</v>
+        <v>313.7385755734219</v>
       </c>
       <c r="N364" t="n">
-        <v>195.6875572667103</v>
+        <v>195.6875572667105</v>
       </c>
       <c r="O364" t="n">
-        <v>58.8740057771773</v>
+        <v>58.87400577717732</v>
       </c>
       <c r="P364" t="n">
         <v>0</v>
@@ -19792,13 +19792,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M365" t="n">
-        <v>269.4180018568566</v>
+        <v>269.4180018568568</v>
       </c>
       <c r="N365" t="n">
-        <v>167.4668157457644</v>
+        <v>167.4668157457646</v>
       </c>
       <c r="O365" t="n">
-        <v>52.42893477501216</v>
+        <v>52.42893477501221</v>
       </c>
       <c r="P365" t="n">
         <v>0</v>
@@ -19845,13 +19845,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M366" t="n">
-        <v>295.5709577042608</v>
+        <v>295.5709577042597</v>
       </c>
       <c r="N366" t="n">
-        <v>184.1232419606829</v>
+        <v>184.1232419606816</v>
       </c>
       <c r="O366" t="n">
-        <v>56.26259331794689</v>
+        <v>56.26259331794665</v>
       </c>
       <c r="P366" t="n">
         <v>0</v>
@@ -19898,13 +19898,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M367" t="n">
-        <v>308.9601452647034</v>
+        <v>308.9601452647015</v>
       </c>
       <c r="N367" t="n">
-        <v>192.6474033253442</v>
+        <v>192.6474033253419</v>
       </c>
       <c r="O367" t="n">
-        <v>58.19118415977385</v>
+        <v>58.1911841597734</v>
       </c>
       <c r="P367" t="n">
         <v>1</v>
@@ -19951,13 +19951,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M368" t="n">
-        <v>318.5215316861588</v>
+        <v>318.5215316861582</v>
       </c>
       <c r="N368" t="n">
-        <v>198.7333951608811</v>
+        <v>198.7333951608804</v>
       </c>
       <c r="O368" t="n">
-        <v>59.55525999050754</v>
+        <v>59.55525999050742</v>
       </c>
       <c r="P368" t="n">
         <v>0</v>
@@ -20004,13 +20004,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M369" t="n">
-        <v>312.785172492333</v>
+        <v>312.7851724923324</v>
       </c>
       <c r="N369" t="n">
-        <v>195.0823712624704</v>
+        <v>195.0823712624697</v>
       </c>
       <c r="O369" t="n">
-        <v>58.7381889878209</v>
+        <v>58.73818898782077</v>
       </c>
       <c r="P369" t="n">
         <v>0</v>
@@ -20057,13 +20057,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M370" t="n">
-        <v>308.9613558473208</v>
+        <v>308.9613558473211</v>
       </c>
       <c r="N370" t="n">
-        <v>192.6489130090898</v>
+        <v>192.6489130090901</v>
       </c>
       <c r="O370" t="n">
-        <v>58.19146916931155</v>
+        <v>58.19146916931161</v>
       </c>
       <c r="P370" t="n">
         <v>1</v>
@@ -20110,13 +20110,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M371" t="n">
-        <v>306.0956743589131</v>
+        <v>306.0956743589138</v>
       </c>
       <c r="N371" t="n">
-        <v>190.8265550798605</v>
+        <v>190.8265550798614</v>
       </c>
       <c r="O371" t="n">
-        <v>57.78082030891461</v>
+        <v>57.78082030891476</v>
       </c>
       <c r="P371" t="n">
         <v>1</v>
@@ -20163,13 +20163,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M372" t="n">
-        <v>313.7407068113867</v>
+        <v>313.7407068113878</v>
       </c>
       <c r="N372" t="n">
-        <v>195.6902159016397</v>
+        <v>195.6902159016411</v>
       </c>
       <c r="O372" t="n">
-        <v>58.87450569427618</v>
+        <v>58.87450569427645</v>
       </c>
       <c r="P372" t="n">
         <v>0</v>
@@ -20216,13 +20216,13 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="M373" t="n">
-        <v>319.4758137848008</v>
+        <v>319.4758137848015</v>
       </c>
       <c r="N373" t="n">
-        <v>199.3396857791376</v>
+        <v>199.3396857791385</v>
       </c>
       <c r="O373" t="n">
-        <v>59.69066000328755</v>
+        <v>59.6906600032877</v>
       </c>
       <c r="P373" t="n">
         <v>0</v>
